--- a/templates/UW_Model_Template.xlsx
+++ b/templates/UW_Model_Template.xlsx
@@ -10,11 +10,13 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="RR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="P&amp;L" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pro Forma" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sources &amp; Uses" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Debt" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Returns" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Renovation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="P&amp;L" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pro Forma" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sources &amp; Uses" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Debt" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Returns" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Sensitivity" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,8 +106,20 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -127,8 +141,13 @@
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -144,11 +163,25 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -172,12 +205,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -187,22 +221,44 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -568,17 +624,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Multifamily UW Model  —  Starter Template</t>
+          <t>Multifamily UW Model  —  Starter Template (v2)</t>
         </is>
       </c>
     </row>
@@ -590,7 +646,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row r="4" ht="25" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Legend</t>
@@ -602,7 +658,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="26" customHeight="1">
+    <row r="5" ht="25" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Fill order</t>
@@ -610,7 +666,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1) Assumptions  2) RR (rent roll)  3) P&amp;L (enter in-place expenses)  4) review Pro Forma / Debt / Returns (all auto-calc).</t>
+          <t>1) Assumptions  2) RR (rent roll)  3) Renovation (value-add scope &amp; timing)  4) P&amp;L (enter in-place expenses)  5) review Pro Forma / Debt / Returns / Sensitivity (all auto-calc).</t>
         </is>
       </c>
     </row>
@@ -621,12 +677,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HOW THE TABS CONNECT (the model is one chain)</t>
+          <t>HOW THE TABS CONNECT (one chain)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="26" customHeight="1">
+    <row r="8" ht="37.5" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Assumptions</t>
@@ -634,11 +690,11 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>The control panel. Every lever lives here once — growth, vacancy, cap rates, LTV, rate, hold. Every other tab reads these cells, so you change a deal from this one tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="39" customHeight="1">
+          <t>Control panel. Every lever lives here once — growth, vacancy, cap rates, LTV, rate, and HOLD PERIOD (1-10 yrs; the model exits automatically in the hold year). Change a deal from this one tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>RR  (Rent Roll)</t>
@@ -646,83 +702,91 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Unit-level income engine. Unit mix x in-place rent = in-place Gross Potential Rent (GPR); unit mix x market rent = market GPR. Feeds the top line of P&amp;L. Total unit count also flows to Assumptions and the per-unit metrics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
+          <t>Unit-level income engine. Unit mix x in-place rent = in-place GPR; unit mix x market rent = as-is market GPR. Feeds the P&amp;L top line and the unit count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62.5" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Renovation  (value-add)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>The value-add engine. Per unit type: how many units you renovate, the cost/unit, and the rent premium/unit achieved ABOVE market. Sums to a total renovation budget (-&gt; Sources &amp; Uses) and a rent-premium schedule phased by your completion %/year (-&gt; Pro Forma). Capex is funded upfront in the capital stack; the timing row shows when the budget is drawn and when the premium is earned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="37.5" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>P&amp;L  (Operating Statement)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Turns rent into cash flow. GPR (from RR)  - vacancy &amp; bad debt  + other income = EGI;  EGI - operating expenses = NOI. Two columns: In-Place (T-12 actuals you type) and Year-1 Underwritten (market rents from RR, expenses grown &amp; re-based per Assumptions). NOI is the single most important number in the model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="39" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Pro Forma</t>
-        </is>
-      </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Projects the Year-1 underwritten EGI and OpEx from P&amp;L across the hold using the growth rates in Assumptions. Produces NOI for each year — the cash the property throws off before financing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39" customHeight="1">
+          <t>Turns rent into cash flow. GPR (from RR) - vacancy &amp; bad debt + other income = EGI; EGI - operating expenses = NOI. Two columns: In-Place (T-12 you type) and Year-1 Underwritten (as-is market). NOI is the single most important number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Pro Forma (10-yr)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Projects Year-1 underwritten EGI &amp; OpEx across up to 10 years using the growth rates, then LAYERS ON the renovation premium schedule -&gt; NOI each year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>Sources &amp; Uses</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>The capital stack. Uses = purchase price + closing costs + capex (from Assumptions). Sources = senior loan (LTV x price) + equity (the plug). Equity here is the check the investor writes — it anchors every return metric.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Capital stack. Uses = price + closing + renovation budget (from Renovation). Sources = senior loan (LTV x price) + equity (the plug). Equity anchors returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Sizes the loan from Sources &amp; Uses and amortizes it: annual debt service, DSCR (NOI / debt service), debt yield, and the loan payoff balance at exit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Sizes &amp; amortizes the loan: annual debt service, DSCR, debt yield, and the loan payoff balance in the hold year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="37.5" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Ties it all together. Levered cash flow = Pro Forma NOI - debt service each year; exit value = final-year NOI / exit cap; net sale proceeds repay the loan. From the equity outflow (Sources &amp; Uses) and these inflows it computes IRR, equity multiple, and cash-on-cash — both levered and unlevered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="39" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Ties it together, exiting in your chosen hold year: levered CF = Pro Forma NOI - debt service; exit value = hold-year NOI / exit cap; proceeds repay the loan -&gt; IRR, equity multiple, cash-on-cash (levered &amp; unlevered).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="37.5" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>One sentence</t>
+          <t>Sensitivity</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>RR builds income -&gt; P&amp;L converts it to NOI -&gt; Pro Forma grows NOI -&gt; Sources &amp; Uses and Debt set the capital -&gt; Returns measures what the equity earns. Change an Assumption and the whole chain re-solves.</t>
+          <t>A 2-way grid of levered IRR across Exit Cap (columns) x Rent Growth (rows). It re-runs the full levered cash flow for each combination via backing calcs below the grid, so it updates live when you change the deal. The center cell equals the Returns tab IRR.</t>
         </is>
       </c>
     </row>
@@ -730,21 +794,1766 @@
       <c r="A17" s="5" t="inlineStr"/>
       <c r="B17" s="3" t="inlineStr"/>
     </row>
-    <row r="18" ht="26" customHeight="1">
+    <row r="18" ht="37.5" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>One sentence</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>RR + Renovation build income -&gt; P&amp;L converts it to NOI -&gt; Pro Forma grows &amp; renovates NOI over the hold -&gt; Sources &amp; Uses and Debt set the capital -&gt; Returns measures the equity's IRR -&gt; Sensitivity stress-tests it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="37.5" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Renovation funding note</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>The renovation budget is included in Uses and funded at close (equity + loan), so it is NOT subtracted again from operating cash flow. The Renovation timing row is informational (draw schedule) and drives WHEN the rent premium is realized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>This is a teaching/starter template with illustrative numbers (a ~100-unit deal). Replace every blue/yellow cell with your deal's data. It is not investment advice.</t>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Teaching/starter template with illustrative numbers (a ~100-unit value-add deal). Replace every blue/yellow cell with your deal's data. Not investment advice.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity  —  Levered IRR:  Exit Cap (cols) x Rent Growth (rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>Growth \ Exit Cap</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D5" s="44" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E5" s="44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F5" s="44" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G5" s="44" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C6" s="46">
+        <f>B$33</f>
+        <v/>
+      </c>
+      <c r="D6" s="46">
+        <f>C$33</f>
+        <v/>
+      </c>
+      <c r="E6" s="46">
+        <f>D$33</f>
+        <v/>
+      </c>
+      <c r="F6" s="46">
+        <f>E$33</f>
+        <v/>
+      </c>
+      <c r="G6" s="46">
+        <f>F$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C7" s="46">
+        <f>G$33</f>
+        <v/>
+      </c>
+      <c r="D7" s="46">
+        <f>H$33</f>
+        <v/>
+      </c>
+      <c r="E7" s="46">
+        <f>I$33</f>
+        <v/>
+      </c>
+      <c r="F7" s="46">
+        <f>J$33</f>
+        <v/>
+      </c>
+      <c r="G7" s="46">
+        <f>K$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="45" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C8" s="46">
+        <f>L$33</f>
+        <v/>
+      </c>
+      <c r="D8" s="46">
+        <f>M$33</f>
+        <v/>
+      </c>
+      <c r="E8" s="47">
+        <f>N$33</f>
+        <v/>
+      </c>
+      <c r="F8" s="46">
+        <f>O$33</f>
+        <v/>
+      </c>
+      <c r="G8" s="46">
+        <f>P$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="45" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C9" s="46">
+        <f>Q$33</f>
+        <v/>
+      </c>
+      <c r="D9" s="46">
+        <f>R$33</f>
+        <v/>
+      </c>
+      <c r="E9" s="46">
+        <f>S$33</f>
+        <v/>
+      </c>
+      <c r="F9" s="46">
+        <f>T$33</f>
+        <v/>
+      </c>
+      <c r="G9" s="46">
+        <f>U$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C10" s="46">
+        <f>V$33</f>
+        <v/>
+      </c>
+      <c r="D10" s="46">
+        <f>W$33</f>
+        <v/>
+      </c>
+      <c r="E10" s="46">
+        <f>X$33</f>
+        <v/>
+      </c>
+      <c r="F10" s="46">
+        <f>Y$33</f>
+        <v/>
+      </c>
+      <c r="G10" s="46">
+        <f>Z$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Center cell (3% / 6.0%) = Returns levered IRR. Green shading is your base case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>BACKING CALCULATIONS (do not edit) — one column per scenario</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="O19" s="7" t="n"/>
+      <c r="P19" s="7" t="n"/>
+      <c r="Q19" s="7" t="n"/>
+      <c r="R19" s="7" t="n"/>
+      <c r="S19" s="7" t="n"/>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
+      <c r="W19" s="7" t="n"/>
+      <c r="X19" s="7" t="n"/>
+      <c r="Y19" s="7" t="n"/>
+      <c r="Z19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Rent Growth (g)</t>
+        </is>
+      </c>
+      <c r="B20" s="13">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C20" s="13">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="D20" s="13">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="E20" s="13">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F20" s="13">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="G20" s="13">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="H20" s="13">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="I20" s="13">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="J20" s="13">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="K20" s="13">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="L20" s="13">
+        <f>$B$8</f>
+        <v/>
+      </c>
+      <c r="M20" s="13">
+        <f>$B$8</f>
+        <v/>
+      </c>
+      <c r="N20" s="13">
+        <f>$B$8</f>
+        <v/>
+      </c>
+      <c r="O20" s="13">
+        <f>$B$8</f>
+        <v/>
+      </c>
+      <c r="P20" s="13">
+        <f>$B$8</f>
+        <v/>
+      </c>
+      <c r="Q20" s="13">
+        <f>$B$9</f>
+        <v/>
+      </c>
+      <c r="R20" s="13">
+        <f>$B$9</f>
+        <v/>
+      </c>
+      <c r="S20" s="13">
+        <f>$B$9</f>
+        <v/>
+      </c>
+      <c r="T20" s="13">
+        <f>$B$9</f>
+        <v/>
+      </c>
+      <c r="U20" s="13">
+        <f>$B$9</f>
+        <v/>
+      </c>
+      <c r="V20" s="13">
+        <f>$B$10</f>
+        <v/>
+      </c>
+      <c r="W20" s="13">
+        <f>$B$10</f>
+        <v/>
+      </c>
+      <c r="X20" s="13">
+        <f>$B$10</f>
+        <v/>
+      </c>
+      <c r="Y20" s="13">
+        <f>$B$10</f>
+        <v/>
+      </c>
+      <c r="Z20" s="13">
+        <f>$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Exit Cap (X)</t>
+        </is>
+      </c>
+      <c r="B21" s="13">
+        <f>C$5</f>
+        <v/>
+      </c>
+      <c r="C21" s="13">
+        <f>D$5</f>
+        <v/>
+      </c>
+      <c r="D21" s="13">
+        <f>E$5</f>
+        <v/>
+      </c>
+      <c r="E21" s="13">
+        <f>F$5</f>
+        <v/>
+      </c>
+      <c r="F21" s="13">
+        <f>G$5</f>
+        <v/>
+      </c>
+      <c r="G21" s="13">
+        <f>C$5</f>
+        <v/>
+      </c>
+      <c r="H21" s="13">
+        <f>D$5</f>
+        <v/>
+      </c>
+      <c r="I21" s="13">
+        <f>E$5</f>
+        <v/>
+      </c>
+      <c r="J21" s="13">
+        <f>F$5</f>
+        <v/>
+      </c>
+      <c r="K21" s="13">
+        <f>G$5</f>
+        <v/>
+      </c>
+      <c r="L21" s="13">
+        <f>C$5</f>
+        <v/>
+      </c>
+      <c r="M21" s="13">
+        <f>D$5</f>
+        <v/>
+      </c>
+      <c r="N21" s="13">
+        <f>E$5</f>
+        <v/>
+      </c>
+      <c r="O21" s="13">
+        <f>F$5</f>
+        <v/>
+      </c>
+      <c r="P21" s="13">
+        <f>G$5</f>
+        <v/>
+      </c>
+      <c r="Q21" s="13">
+        <f>C$5</f>
+        <v/>
+      </c>
+      <c r="R21" s="13">
+        <f>D$5</f>
+        <v/>
+      </c>
+      <c r="S21" s="13">
+        <f>E$5</f>
+        <v/>
+      </c>
+      <c r="T21" s="13">
+        <f>F$5</f>
+        <v/>
+      </c>
+      <c r="U21" s="13">
+        <f>G$5</f>
+        <v/>
+      </c>
+      <c r="V21" s="13">
+        <f>C$5</f>
+        <v/>
+      </c>
+      <c r="W21" s="13">
+        <f>D$5</f>
+        <v/>
+      </c>
+      <c r="X21" s="13">
+        <f>E$5</f>
+        <v/>
+      </c>
+      <c r="Y21" s="13">
+        <f>F$5</f>
+        <v/>
+      </c>
+      <c r="Z21" s="13">
+        <f>G$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 0</t>
+        </is>
+      </c>
+      <c r="B22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="C22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="D22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="E22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="F22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="G22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="H22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="I22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="L22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="N22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="O22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="P22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="Q22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="R22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="S22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="T22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="U22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="V22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="W22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="X22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="Y22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="Z22" s="12">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 1</t>
+        </is>
+      </c>
+      <c r="B23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="12">
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 2</t>
+        </is>
+      </c>
+      <c r="B24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="12">
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 3</t>
+        </is>
+      </c>
+      <c r="B25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="12">
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="12">
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 5</t>
+        </is>
+      </c>
+      <c r="B27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="12">
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 6</t>
+        </is>
+      </c>
+      <c r="B28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="12">
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 7</t>
+        </is>
+      </c>
+      <c r="B29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z29" s="12">
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 8</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z30" s="12">
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 9</t>
+        </is>
+      </c>
+      <c r="B31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z31" s="12">
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>CF Year 10</t>
+        </is>
+      </c>
+      <c r="B32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="C32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="M32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="N32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="O32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="P32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="R32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="S32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="U32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="V32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="W32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="X32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Y32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="Z32" s="12">
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="B33" s="32">
+        <f>IRR(B22:B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="32">
+        <f>IRR(C22:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="32">
+        <f>IRR(D22:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="32">
+        <f>IRR(E22:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="32">
+        <f>IRR(F22:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="32">
+        <f>IRR(G22:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="32">
+        <f>IRR(H22:H32)</f>
+        <v/>
+      </c>
+      <c r="I33" s="32">
+        <f>IRR(I22:I32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="32">
+        <f>IRR(J22:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="32">
+        <f>IRR(K22:K32)</f>
+        <v/>
+      </c>
+      <c r="L33" s="32">
+        <f>IRR(L22:L32)</f>
+        <v/>
+      </c>
+      <c r="M33" s="32">
+        <f>IRR(M22:M32)</f>
+        <v/>
+      </c>
+      <c r="N33" s="32">
+        <f>IRR(N22:N32)</f>
+        <v/>
+      </c>
+      <c r="O33" s="32">
+        <f>IRR(O22:O32)</f>
+        <v/>
+      </c>
+      <c r="P33" s="32">
+        <f>IRR(P22:P32)</f>
+        <v/>
+      </c>
+      <c r="Q33" s="32">
+        <f>IRR(Q22:Q32)</f>
+        <v/>
+      </c>
+      <c r="R33" s="32">
+        <f>IRR(R22:R32)</f>
+        <v/>
+      </c>
+      <c r="S33" s="32">
+        <f>IRR(S22:S32)</f>
+        <v/>
+      </c>
+      <c r="T33" s="32">
+        <f>IRR(T22:T32)</f>
+        <v/>
+      </c>
+      <c r="U33" s="32">
+        <f>IRR(U22:U32)</f>
+        <v/>
+      </c>
+      <c r="V33" s="32">
+        <f>IRR(V22:V32)</f>
+        <v/>
+      </c>
+      <c r="W33" s="32">
+        <f>IRR(W22:W32)</f>
+        <v/>
+      </c>
+      <c r="X33" s="32">
+        <f>IRR(X22:X32)</f>
+        <v/>
+      </c>
+      <c r="Y33" s="32">
+        <f>IRR(Y22:Y32)</f>
+        <v/>
+      </c>
+      <c r="Z33" s="32">
+        <f>IRR(Z22:Z32)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -761,7 +2570,7 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -820,7 +2629,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Going-in Cap Rate (Yr1 UW)</t>
+          <t>Going-in Cap (as-is, Yr1 UW)</t>
         </is>
       </c>
       <c r="B7" s="13">
@@ -829,18 +2638,23 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Auto: Year-1 underwritten NOI / price.</t>
+          <t>Auto: Year-1 as-is underwritten NOI / price (excludes reno upside).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Hold Period (years)</t>
+          <t>Hold Period (years, 1-10)</t>
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Model exits automatically in this year (max 10).</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -916,11 +2730,6 @@
       <c r="B16" s="15" t="n">
         <v>0.05</v>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Physical + economic loss vs. gross potential rent.</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -999,11 +2808,17 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Renovation / Capex Budget</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>1000000</v>
+          <t>Renovation Budget (auto)</t>
+        </is>
+      </c>
+      <c r="B25" s="19">
+        <f>'Renovation'!$E$9</f>
+        <v/>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Totals up from the Renovation tab scope.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1023,15 +2838,15 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1042,52 +2857,52 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Unit Type</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t># Units</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Avg SF</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>In-Place Rent
 ($/unit/mo)</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Market Rent
 ($/unit/mo)</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>In-Place
 Monthly</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>In-Place
 Annual</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>Market
 Monthly</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>Market
 Annual</t>
@@ -1235,51 +3050,51 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Total / Weighted</t>
         </is>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="22">
         <f>SUM(B4:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="22">
         <f>SUMPRODUCT(B4:B7,C4:C7)/B8</f>
         <v/>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <f>F8/B8</f>
         <v/>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="23">
         <f>H8/B8</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <f>SUM(F4:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="24">
         <f>SUM(G4:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="24">
         <f>SUM(H4:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="24">
         <f>SUM(I4:I7)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Loss-to-Lease (Market - In-Place, annual)</t>
         </is>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="26">
         <f>I8-G8</f>
         <v/>
       </c>
@@ -1298,448 +3113,476 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>P&amp;L  —  Operating Statement  (income -&gt; NOI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>Line Item</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>In-Place (T-12)</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>Year-1 Underwritten</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>Per Unit (UW)</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>INCOME</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
+          <t>Renovation  —  value-add scope, budget &amp; timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>RENOVATION SCOPE (by unit type)</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Unit Type</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t># Units to Reno</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Reno Cost/Unit</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Rent Premium ($/mo)</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Reno Budget</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Annual Premium (gross)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Gross Potential Rent (GPR)</t>
-        </is>
-      </c>
-      <c r="B5" s="26">
-        <f>'RR'!$G$8</f>
-        <v/>
-      </c>
-      <c r="C5" s="26">
-        <f>'RR'!$I$8</f>
-        <v/>
-      </c>
-      <c r="D5" s="12">
-        <f>C5/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E5" s="27" t="inlineStr">
-        <is>
-          <t>In-place=RR in-place annual; UW=RR market annual.</t>
-        </is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="E5" s="12">
+        <f>B5*C5</f>
+        <v/>
+      </c>
+      <c r="F5" s="12">
+        <f>B5*D5*12</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Less: Vacancy</t>
-        </is>
-      </c>
-      <c r="B6" s="12">
-        <f>-B5*'Assumptions'!$B$16</f>
-        <v/>
-      </c>
-      <c r="C6" s="12">
-        <f>-C5*'Assumptions'!$B$16</f>
-        <v/>
-      </c>
-      <c r="D6" s="12">
-        <f>C6/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E6" s="27" t="inlineStr">
-        <is>
-          <t>Economic vacancy from Assumptions.</t>
-        </is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="E6" s="12">
+        <f>B6*C6</f>
+        <v/>
+      </c>
+      <c r="F6" s="12">
+        <f>B6*D6*12</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Less: Bad Debt &amp; Concessions</t>
-        </is>
-      </c>
-      <c r="B7" s="12">
-        <f>-B5*'Assumptions'!$B$17</f>
-        <v/>
-      </c>
-      <c r="C7" s="12">
-        <f>-C5*'Assumptions'!$B$17</f>
-        <v/>
-      </c>
-      <c r="D7" s="12">
-        <f>C7/'RR'!$B$8</f>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="12">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>B7*D7*12</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Net Rental Income</t>
-        </is>
-      </c>
-      <c r="B8" s="22">
-        <f>SUM(B5:B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="22">
-        <f>SUM(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="12">
-        <f>C8/'RR'!$B$8</f>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>225</v>
+      </c>
+      <c r="E8" s="12">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>B8*D8*12</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Other Income (RUBS, fees, laundry)</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C9" s="12">
-        <f>B9*(1+'Assumptions'!$B$14)</f>
-        <v/>
-      </c>
-      <c r="D9" s="12">
-        <f>C9/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>Type T-12 actual; UW grows it one year.</t>
-        </is>
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="27">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>SUM(E5:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="24">
+        <f>SUM(F5:F8)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Effective Gross Income (EGI)</t>
-        </is>
-      </c>
-      <c r="B10" s="22">
-        <f>B8+B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="22">
-        <f>C8+C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="12">
-        <f>C10/'RR'!$B$8</f>
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Blended cost / renovated unit</t>
+        </is>
+      </c>
+      <c r="E10" s="12">
+        <f>E9/B9</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>RENOVATION TIMING (phased)</t>
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Property Taxes</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>165000</v>
-      </c>
-      <c r="C13" s="12">
-        <f>B13*(1+'Assumptions'!$B$15)</f>
-        <v/>
-      </c>
-      <c r="D13" s="12">
-        <f>C13/'RR'!$B$8</f>
-        <v/>
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" s="28" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="n">
-        <v>55000</v>
-      </c>
-      <c r="C14" s="12">
-        <f>B14*(1+'Assumptions'!$B$15)</f>
-        <v/>
-      </c>
-      <c r="D14" s="12">
-        <f>C14/'RR'!$B$8</f>
-        <v/>
+          <t>% of Scope Complete (cumulative)</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>120000</v>
-      </c>
-      <c r="C15" s="12">
-        <f>B15*(1+'Assumptions'!$B$15)</f>
-        <v/>
-      </c>
-      <c r="D15" s="12">
-        <f>C15/'RR'!$B$8</f>
+          <t>Cumulative Units Renovated</t>
+        </is>
+      </c>
+      <c r="B15" s="29">
+        <f>$B$9*B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="29">
+        <f>$B$9*C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="29">
+        <f>$B$9*D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="29">
+        <f>$B$9*E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="29">
+        <f>$B$9*F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="29">
+        <f>$B$9*G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="29">
+        <f>$B$9*H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="29">
+        <f>$B$9*I14</f>
+        <v/>
+      </c>
+      <c r="J15" s="29">
+        <f>$B$9*J14</f>
+        <v/>
+      </c>
+      <c r="K15" s="29">
+        <f>$B$9*K14</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n">
-        <v>95000</v>
+          <t>Reno Capex Draw ($)</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>$E$9*B14</f>
+        <v/>
       </c>
       <c r="C16" s="12">
-        <f>B16*(1+'Assumptions'!$B$15)</f>
+        <f>$E$9*(C14-B14)</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>C16/'RR'!$B$8</f>
+        <f>$E$9*(D14-C14)</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
+        <f>$E$9*(E14-D14)</f>
+        <v/>
+      </c>
+      <c r="F16" s="12">
+        <f>$E$9*(F14-E14)</f>
+        <v/>
+      </c>
+      <c r="G16" s="12">
+        <f>$E$9*(G14-F14)</f>
+        <v/>
+      </c>
+      <c r="H16" s="12">
+        <f>$E$9*(H14-G14)</f>
+        <v/>
+      </c>
+      <c r="I16" s="12">
+        <f>$E$9*(I14-H14)</f>
+        <v/>
+      </c>
+      <c r="J16" s="12">
+        <f>$E$9*(J14-I14)</f>
+        <v/>
+      </c>
+      <c r="K16" s="12">
+        <f>$E$9*(K14-J14)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>140000</v>
+          <t>Cumulative Premium (gross annual)</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>$F$9*B14</f>
+        <v/>
       </c>
       <c r="C17" s="12">
-        <f>B17*(1+'Assumptions'!$B$15)</f>
+        <f>$F$9*C14</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>C17/'RR'!$B$8</f>
+        <f>$F$9*D14</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>$F$9*E14</f>
+        <v/>
+      </c>
+      <c r="F17" s="12">
+        <f>$F$9*F14</f>
+        <v/>
+      </c>
+      <c r="G17" s="12">
+        <f>$F$9*G14</f>
+        <v/>
+      </c>
+      <c r="H17" s="12">
+        <f>$F$9*H14</f>
+        <v/>
+      </c>
+      <c r="I17" s="12">
+        <f>$F$9*I14</f>
+        <v/>
+      </c>
+      <c r="J17" s="12">
+        <f>$F$9*J14</f>
+        <v/>
+      </c>
+      <c r="K17" s="12">
+        <f>$F$9*K14</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Contract Services</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n">
-        <v>45000</v>
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Net Premium to EGI</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>B17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
+        <v/>
       </c>
       <c r="C18" s="12">
-        <f>B18*(1+'Assumptions'!$B$15)</f>
+        <f>C17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>C18/'RR'!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Leasing</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C19" s="12">
-        <f>B19*(1+'Assumptions'!$B$15)</f>
-        <v/>
-      </c>
-      <c r="D19" s="12">
-        <f>C19/'RR'!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>General &amp; Admin</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C20" s="12">
-        <f>B20*(1+'Assumptions'!$B$15)</f>
-        <v/>
-      </c>
-      <c r="D20" s="12">
-        <f>C20/'RR'!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Management Fee (% of EGI)</t>
-        </is>
-      </c>
-      <c r="B21" s="12">
-        <f>B10*'Assumptions'!$B$18</f>
-        <v/>
-      </c>
-      <c r="C21" s="12">
-        <f>C10*'Assumptions'!$B$18</f>
-        <v/>
-      </c>
-      <c r="D21" s="12">
-        <f>C21/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
-        <is>
-          <t>Computed as % of EGI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Replacement Reserves</t>
-        </is>
-      </c>
-      <c r="B22" s="26">
-        <f>'RR'!$B$8*'Assumptions'!$B$19</f>
-        <v/>
-      </c>
-      <c r="C22" s="26">
-        <f>'RR'!$B$8*'Assumptions'!$B$19</f>
-        <v/>
-      </c>
-      <c r="D22" s="12">
-        <f>C22/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>Units x reserves/unit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B23" s="23">
-        <f>SUM(B13:B22)</f>
-        <v/>
-      </c>
-      <c r="C23" s="23">
-        <f>SUM(C13:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="12">
-        <f>C23/'RR'!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>NET OPERATING INCOME (NOI)</t>
-        </is>
-      </c>
-      <c r="B24" s="28">
-        <f>B10-B23</f>
-        <v/>
-      </c>
-      <c r="C24" s="28">
-        <f>C10-C23</f>
-        <v/>
-      </c>
-      <c r="D24" s="12">
-        <f>C24/'RR'!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Operating Expense Ratio</t>
-        </is>
-      </c>
-      <c r="B25" s="13">
-        <f>B23/B10</f>
-        <v/>
-      </c>
-      <c r="C25" s="13">
-        <f>C23/C10</f>
+        <f>D17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>E17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="12">
+        <f>F17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="12">
+        <f>G17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="12">
+        <f>H17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="12">
+        <f>I17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="12">
+        <f>J17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="12">
+        <f>K17*(1-'Assumptions'!$B$16-'Assumptions'!$B$17)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1751,168 +3594,450 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Pro Forma  —  NOI projection over the hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+          <t>P&amp;L  —  Operating Statement  (income -&gt; NOI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="D3" s="29" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="F3" s="29" t="inlineStr">
-        <is>
-          <t>Year 5</t>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>In-Place (T-12)</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Year-1 Underwritten</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Per Unit (UW)</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Effective Gross Income</t>
-        </is>
-      </c>
-      <c r="B4" s="26">
-        <f>'P&amp;L'!$C$10</f>
-        <v/>
-      </c>
-      <c r="C4" s="12">
-        <f>B4*(1+'Assumptions'!$B$14)</f>
-        <v/>
-      </c>
-      <c r="D4" s="12">
-        <f>C4*(1+'Assumptions'!$B$14)</f>
-        <v/>
-      </c>
-      <c r="E4" s="12">
-        <f>D4*(1+'Assumptions'!$B$14)</f>
-        <v/>
-      </c>
-      <c r="F4" s="12">
-        <f>E4*(1+'Assumptions'!$B$14)</f>
-        <v/>
-      </c>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B5" s="26">
-        <f>'P&amp;L'!$C$23</f>
-        <v/>
-      </c>
-      <c r="C5" s="12">
-        <f>B5*(1+'Assumptions'!$B$15)</f>
-        <v/>
+          <t>Gross Potential Rent (GPR)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>'RR'!$G$8</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>'RR'!$I$8</t>
+        </is>
       </c>
       <c r="D5" s="12">
-        <f>C5*(1+'Assumptions'!$B$15)</f>
-        <v/>
-      </c>
-      <c r="E5" s="12">
-        <f>D5*(1+'Assumptions'!$B$15)</f>
-        <v/>
-      </c>
-      <c r="F5" s="12">
-        <f>E5*(1+'Assumptions'!$B$15)</f>
-        <v/>
+        <f>C5/'RR'!$B$8</f>
+        <v/>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
+        <is>
+          <t>In-place=RR in-place annual; UW=RR as-is market annual.</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="B6" s="23">
-        <f>B4-B5</f>
-        <v/>
-      </c>
-      <c r="C6" s="23">
-        <f>C4-C5</f>
-        <v/>
-      </c>
-      <c r="D6" s="23">
-        <f>D4-D5</f>
-        <v/>
-      </c>
-      <c r="E6" s="23">
-        <f>E4-E5</f>
-        <v/>
-      </c>
-      <c r="F6" s="23">
-        <f>F4-F5</f>
-        <v/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Less: Vacancy</t>
+        </is>
+      </c>
+      <c r="B6" s="12">
+        <f>-B5*'Assumptions'!$B$16</f>
+        <v/>
+      </c>
+      <c r="C6" s="12">
+        <f>-C5*'Assumptions'!$B$16</f>
+        <v/>
+      </c>
+      <c r="D6" s="12">
+        <f>C6/'RR'!$B$8</f>
+        <v/>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>Economic vacancy.</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>NOI Growth %</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C7" s="13">
-        <f>C6/B6-1</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>D6/C6-1</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>E6/D6-1</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>F6/E6-1</f>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Less: Bad Debt &amp; Concessions</t>
+        </is>
+      </c>
+      <c r="B7" s="12">
+        <f>-B5*'Assumptions'!$B$17</f>
+        <v/>
+      </c>
+      <c r="C7" s="12">
+        <f>-C5*'Assumptions'!$B$17</f>
+        <v/>
+      </c>
+      <c r="D7" s="12">
+        <f>C7/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Net Rental Income</t>
+        </is>
+      </c>
+      <c r="B8" s="23">
+        <f>SUM(B5:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="23">
+        <f>SUM(C5:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="12">
+        <f>C8/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Other Income (RUBS, fees, laundry)</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C9" s="12">
+        <f>B9*(1+'Assumptions'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="D9" s="12">
+        <f>C9/'RR'!$B$8</f>
+        <v/>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>Type T-12 actual; UW grows it one year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Effective Gross Income (EGI)</t>
+        </is>
+      </c>
+      <c r="B10" s="23">
+        <f>B8+B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="23">
+        <f>C8+C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="12">
+        <f>C10/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Property Taxes</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>165000</v>
+      </c>
+      <c r="C13" s="12">
+        <f>B13*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="D13" s="12">
+        <f>C13/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C14" s="12">
+        <f>B14*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="D14" s="12">
+        <f>C14/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C15" s="12">
+        <f>B15*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="12">
+        <f>C15/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>95000</v>
+      </c>
+      <c r="C16" s="12">
+        <f>B16*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="12">
+        <f>C16/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>140000</v>
+      </c>
+      <c r="C17" s="12">
+        <f>B17*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="D17" s="12">
+        <f>C17/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Contract Services</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C18" s="12">
+        <f>B18*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="D18" s="12">
+        <f>C18/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Leasing</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C19" s="12">
+        <f>B19*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="D19" s="12">
+        <f>C19/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>General &amp; Admin</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C20" s="12">
+        <f>B20*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="D20" s="12">
+        <f>C20/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Management Fee (% of EGI)</t>
+        </is>
+      </c>
+      <c r="B21" s="12">
+        <f>B10*'Assumptions'!$B$18</f>
+        <v/>
+      </c>
+      <c r="C21" s="12">
+        <f>C10*'Assumptions'!$B$18</f>
+        <v/>
+      </c>
+      <c r="D21" s="12">
+        <f>C21/'RR'!$B$8</f>
+        <v/>
+      </c>
+      <c r="E21" s="30" t="inlineStr">
+        <is>
+          <t>Computed as % of EGI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Replacement Reserves</t>
+        </is>
+      </c>
+      <c r="B22" s="19">
+        <f>'RR'!$B$8*'Assumptions'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C22" s="19">
+        <f>'RR'!$B$8*'Assumptions'!$B$19</f>
+        <v/>
+      </c>
+      <c r="D22" s="12">
+        <f>C22/'RR'!$B$8</f>
+        <v/>
+      </c>
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>Units x reserves/unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B23" s="24">
+        <f>SUM(B13:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="24">
+        <f>SUM(C13:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="12">
+        <f>C23/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>NET OPERATING INCOME (NOI)</t>
+        </is>
+      </c>
+      <c r="B24" s="31">
+        <f>B10-B23</f>
+        <v/>
+      </c>
+      <c r="C24" s="31">
+        <f>C10-C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="12">
+        <f>C24/'RR'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Operating Expense Ratio</t>
+        </is>
+      </c>
+      <c r="B25" s="32">
+        <f>B23/B10</f>
+        <v/>
+      </c>
+      <c r="C25" s="32">
+        <f>C23/C10</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1924,145 +4049,419 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sources &amp; Uses  —  capital stack</t>
+          <t>Pro Forma  —  NOI projection over the hold (up to 10 yrs)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>USES OF FUNDS</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Year 6</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Year 7</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Year 8</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>Year 9</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="inlineStr">
+        <is>
+          <t>Year 10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Purchase Price</t>
-        </is>
-      </c>
-      <c r="B4" s="26">
-        <f>'Assumptions'!$B$4</f>
+          <t>Base EGI (organic)</t>
+        </is>
+      </c>
+      <c r="B4" s="19">
+        <f>'P&amp;L'!$C$10</f>
+        <v/>
+      </c>
+      <c r="C4" s="12">
+        <f>B4*(1+'Assumptions'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="D4" s="12">
+        <f>C4*(1+'Assumptions'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="E4" s="12">
+        <f>D4*(1+'Assumptions'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="F4" s="12">
+        <f>E4*(1+'Assumptions'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="G4" s="12">
+        <f>F4*(1+'Assumptions'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="H4" s="12">
+        <f>G4*(1+'Assumptions'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="I4" s="12">
+        <f>H4*(1+'Assumptions'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="J4" s="12">
+        <f>I4*(1+'Assumptions'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="K4" s="12">
+        <f>J4*(1+'Assumptions'!$B$14)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Closing Costs</t>
-        </is>
-      </c>
-      <c r="B5" s="12">
-        <f>'Assumptions'!$B$4*'Assumptions'!$B$11</f>
+          <t>+ Renovation Premium (net)</t>
+        </is>
+      </c>
+      <c r="B5" s="19">
+        <f>'Renovation'!B18</f>
+        <v/>
+      </c>
+      <c r="C5" s="19">
+        <f>'Renovation'!C18</f>
+        <v/>
+      </c>
+      <c r="D5" s="19">
+        <f>'Renovation'!D18</f>
+        <v/>
+      </c>
+      <c r="E5" s="19">
+        <f>'Renovation'!E18</f>
+        <v/>
+      </c>
+      <c r="F5" s="19">
+        <f>'Renovation'!F18</f>
+        <v/>
+      </c>
+      <c r="G5" s="19">
+        <f>'Renovation'!G18</f>
+        <v/>
+      </c>
+      <c r="H5" s="19">
+        <f>'Renovation'!H18</f>
+        <v/>
+      </c>
+      <c r="I5" s="19">
+        <f>'Renovation'!I18</f>
+        <v/>
+      </c>
+      <c r="J5" s="19">
+        <f>'Renovation'!J18</f>
+        <v/>
+      </c>
+      <c r="K5" s="19">
+        <f>'Renovation'!K18</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Renovation / Capex</t>
-        </is>
-      </c>
-      <c r="B6" s="26">
-        <f>'Assumptions'!$B$25</f>
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Effective Gross Income</t>
+        </is>
+      </c>
+      <c r="B6" s="23">
+        <f>B4+B5</f>
+        <v/>
+      </c>
+      <c r="C6" s="23">
+        <f>C4+C5</f>
+        <v/>
+      </c>
+      <c r="D6" s="23">
+        <f>D4+D5</f>
+        <v/>
+      </c>
+      <c r="E6" s="23">
+        <f>E4+E5</f>
+        <v/>
+      </c>
+      <c r="F6" s="23">
+        <f>F4+F5</f>
+        <v/>
+      </c>
+      <c r="G6" s="23">
+        <f>G4+G5</f>
+        <v/>
+      </c>
+      <c r="H6" s="23">
+        <f>H4+H5</f>
+        <v/>
+      </c>
+      <c r="I6" s="23">
+        <f>I4+I5</f>
+        <v/>
+      </c>
+      <c r="J6" s="23">
+        <f>J4+J5</f>
+        <v/>
+      </c>
+      <c r="K6" s="23">
+        <f>K4+K5</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Total Uses</t>
-        </is>
-      </c>
-      <c r="B7" s="23">
-        <f>SUM(B4:B6)</f>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B7" s="19">
+        <f>'P&amp;L'!$C$23</f>
+        <v/>
+      </c>
+      <c r="C7" s="12">
+        <f>B7*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="D7" s="12">
+        <f>C7*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>D7*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>E7*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>F7*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="H7" s="12">
+        <f>G7*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="I7" s="12">
+        <f>H7*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>I7*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="K7" s="12">
+        <f>J7*(1+'Assumptions'!$B$15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Net Operating Income</t>
+        </is>
+      </c>
+      <c r="B8" s="24">
+        <f>B6-B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="24">
+        <f>C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>D6-D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>E6-E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="24">
+        <f>F6-F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="24">
+        <f>G6-G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="24">
+        <f>H6-H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="24">
+        <f>I6-I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="24">
+        <f>J6-J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="24">
+        <f>K6-K7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>SOURCES OF FUNDS</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>NOI Growth %</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="32">
+        <f>C8/B8-1</f>
+        <v/>
+      </c>
+      <c r="D9" s="32">
+        <f>D8/C8-1</f>
+        <v/>
+      </c>
+      <c r="E9" s="32">
+        <f>E8/D8-1</f>
+        <v/>
+      </c>
+      <c r="F9" s="32">
+        <f>F8/E8-1</f>
+        <v/>
+      </c>
+      <c r="G9" s="32">
+        <f>G8/F8-1</f>
+        <v/>
+      </c>
+      <c r="H9" s="32">
+        <f>H8/G8-1</f>
+        <v/>
+      </c>
+      <c r="I9" s="32">
+        <f>I8/H8-1</f>
+        <v/>
+      </c>
+      <c r="J9" s="32">
+        <f>J8/I8-1</f>
+        <v/>
+      </c>
+      <c r="K9" s="32">
+        <f>K8/J8-1</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Senior Loan</t>
-        </is>
-      </c>
-      <c r="B10" s="12">
-        <f>'Assumptions'!$B$4*'Assumptions'!$B$22</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>B10/B7</f>
-        <v/>
-      </c>
-      <c r="D10" s="10">
-        <f> LTV x Purchase Price</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Equity (plug)</t>
-        </is>
-      </c>
-      <c r="B11" s="12">
-        <f>B7-B10</f>
-        <v/>
-      </c>
-      <c r="C11" s="13">
-        <f>B11/B7</f>
-        <v/>
-      </c>
-      <c r="D11" s="10">
-        <f> the equity check the investor writes</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Total Sources</t>
-        </is>
-      </c>
-      <c r="B12" s="23">
-        <f>SUM(B10:B11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>Check (Sources - Uses)</t>
-        </is>
-      </c>
-      <c r="B14" s="12">
-        <f>B12-B7</f>
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>(memo) Reno Capex Draw</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>'Renovation'!B16</f>
+        <v/>
+      </c>
+      <c r="C10" s="19">
+        <f>'Renovation'!C16</f>
+        <v/>
+      </c>
+      <c r="D10" s="19">
+        <f>'Renovation'!D16</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>'Renovation'!E16</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>'Renovation'!F16</f>
+        <v/>
+      </c>
+      <c r="G10" s="19">
+        <f>'Renovation'!G16</f>
+        <v/>
+      </c>
+      <c r="H10" s="19">
+        <f>'Renovation'!H16</f>
+        <v/>
+      </c>
+      <c r="I10" s="19">
+        <f>'Renovation'!I16</f>
+        <v/>
+      </c>
+      <c r="J10" s="19">
+        <f>'Renovation'!J16</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>'Renovation'!K16</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2074,148 +4473,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Debt  —  loan sizing &amp; amortization</t>
-        </is>
-      </c>
+          <t>Sources &amp; Uses  —  capital stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>USES OF FUNDS</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Loan Amount</t>
-        </is>
-      </c>
-      <c r="B4" s="26">
-        <f>'Sources &amp; Uses'!$B$10</f>
-        <v/>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>From Sources &amp; Uses.</t>
-        </is>
+          <t>Purchase Price</t>
+        </is>
+      </c>
+      <c r="B4" s="19">
+        <f>'Assumptions'!$B$4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
-        </is>
-      </c>
-      <c r="B5" s="31">
-        <f>'Assumptions'!$B$23</f>
+          <t>Closing Costs</t>
+        </is>
+      </c>
+      <c r="B5" s="12">
+        <f>'Assumptions'!$B$4*'Assumptions'!$B$11</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Amortization (years)</t>
-        </is>
-      </c>
-      <c r="B6" s="11">
-        <f>'Assumptions'!$B$24</f>
+          <t>Renovation Budget</t>
+        </is>
+      </c>
+      <c r="B6" s="19">
+        <f>'Renovation'!$E$9</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Hold Period (years)</t>
-        </is>
-      </c>
-      <c r="B7" s="11">
-        <f>'Assumptions'!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Payment</t>
-        </is>
-      </c>
-      <c r="B8" s="32">
-        <f>PMT(B5/12,B6*12,-B4)</f>
-        <v/>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Standard amortizing payment.</t>
-        </is>
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Total Uses</t>
+        </is>
+      </c>
+      <c r="B7" s="24">
+        <f>SUM(B4:B6)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Annual Debt Service</t>
-        </is>
-      </c>
-      <c r="B9" s="23">
-        <f>B8*12</f>
-        <v/>
-      </c>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>SOURCES OF FUNDS</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>DSCR (Year-1 NOI)</t>
-        </is>
-      </c>
-      <c r="B10" s="33">
-        <f>'Pro Forma'!$B$6/B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>NOI / debt service. Lenders want &gt;= ~1.25x.</t>
-        </is>
+          <t>Senior Loan</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>'Assumptions'!$B$4*'Assumptions'!$B$22</f>
+        <v/>
+      </c>
+      <c r="C10" s="32">
+        <f>B10/B7</f>
+        <v/>
+      </c>
+      <c r="D10" s="10">
+        <f> LTV x Purchase Price</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Debt Yield (Year-1 NOI)</t>
-        </is>
-      </c>
-      <c r="B11" s="13">
-        <f>'Pro Forma'!$B$6/B4</f>
-        <v/>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>NOI / loan.</t>
-        </is>
+          <t>Equity (plug)</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>B7-B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="32">
+        <f>B11/B7</f>
+        <v/>
+      </c>
+      <c r="D11" s="10">
+        <f> the equity check the investor writes</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Loan Balance at Exit</t>
-        </is>
-      </c>
-      <c r="B12" s="12">
-        <f>B8*(1-(1+B5/12)^-(B6*12-B7*12))/(B5/12)</f>
-        <v/>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Remaining principal after the hold.</t>
-        </is>
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Total Sources</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>SUM(B10:B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Check (Sources - Uses)</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>B12-B7</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2227,357 +4623,840 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Returns  —  levered &amp; unlevered</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="29" t="inlineStr"/>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>Year 0</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="D3" s="29" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="F3" s="29" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="G3" s="29" t="inlineStr">
-        <is>
-          <t>Year 5</t>
+          <t>Debt  —  loan sizing &amp; amortization</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>NOI (from Pro Forma)</t>
-        </is>
-      </c>
-      <c r="C4" s="26">
-        <f>'Pro Forma'!B6</f>
-        <v/>
-      </c>
-      <c r="D4" s="26">
-        <f>'Pro Forma'!C6</f>
-        <v/>
-      </c>
-      <c r="E4" s="26">
-        <f>'Pro Forma'!D6</f>
-        <v/>
-      </c>
-      <c r="F4" s="26">
-        <f>'Pro Forma'!E6</f>
-        <v/>
-      </c>
-      <c r="G4" s="26">
-        <f>'Pro Forma'!F6</f>
-        <v/>
+          <t>Loan Amount</t>
+        </is>
+      </c>
+      <c r="B4" s="19">
+        <f>'Sources &amp; Uses'!$B$10</f>
+        <v/>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>From Sources &amp; Uses.</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Gross Sale Price (exit)</t>
-        </is>
-      </c>
-      <c r="G5" s="12">
-        <f>G4/'Assumptions'!$B$9</f>
-        <v/>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Interest Rate</t>
+        </is>
+      </c>
+      <c r="B5" s="34">
+        <f>'Assumptions'!$B$23</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Less: Selling Costs</t>
-        </is>
-      </c>
-      <c r="G6" s="12">
-        <f>-G5*'Assumptions'!$B$10</f>
+          <t>Amortization (years)</t>
+        </is>
+      </c>
+      <c r="B6" s="11">
+        <f>'Assumptions'!$B$24</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Less: Loan Payoff</t>
-        </is>
-      </c>
-      <c r="G7" s="12">
-        <f>-'Debt'!$B$12</f>
-        <v/>
+          <t>Hold Period (years)</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>'Assumptions'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Payment</t>
+        </is>
+      </c>
+      <c r="B8" s="35">
+        <f>PMT(B5/12,B6*12,-B4)</f>
+        <v/>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Standard amortizing payment.</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>LEVERED (equity) CASH FLOW</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Annual Debt Service</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>B8*12</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Initial Equity</t>
-        </is>
-      </c>
-      <c r="B10" s="26">
-        <f>-'Sources &amp; Uses'!$B$11</f>
-        <v/>
+          <t>DSCR (Year-1 NOI)</t>
+        </is>
+      </c>
+      <c r="B10" s="37">
+        <f>'Pro Forma'!$B$8/B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>NOI / debt service. Lenders want &gt;= ~1.25x.</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>Debt Yield (Year-1 NOI)</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>'Pro Forma'!$B$8/B4</f>
+        <v/>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>NOI / loan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Loan Balance at Exit</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>B8*(1-(1+B5/12)^-(B6*12-B7*12))/(B5/12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Remaining principal in the hold year.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Returns  —  levered &amp; unlevered (exits in the hold year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Year 0</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Year 6</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Year 7</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>Year 8</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="inlineStr">
+        <is>
+          <t>Year 9</t>
+        </is>
+      </c>
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>Year 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Year #</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" s="38" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>NOI (from Pro Forma)</t>
+        </is>
+      </c>
+      <c r="C5" s="12">
+        <f>IF(AND(C$4&gt;=1,C$4&lt;='Assumptions'!$B$8),'Pro Forma'!B8,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="12">
+        <f>IF(AND(D$4&gt;=1,D$4&lt;='Assumptions'!$B$8),'Pro Forma'!C8,0)</f>
+        <v/>
+      </c>
+      <c r="E5" s="12">
+        <f>IF(AND(E$4&gt;=1,E$4&lt;='Assumptions'!$B$8),'Pro Forma'!D8,0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="12">
+        <f>IF(AND(F$4&gt;=1,F$4&lt;='Assumptions'!$B$8),'Pro Forma'!E8,0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>IF(AND(G$4&gt;=1,G$4&lt;='Assumptions'!$B$8),'Pro Forma'!F8,0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="12">
+        <f>IF(AND(H$4&gt;=1,H$4&lt;='Assumptions'!$B$8),'Pro Forma'!G8,0)</f>
+        <v/>
+      </c>
+      <c r="I5" s="12">
+        <f>IF(AND(I$4&gt;=1,I$4&lt;='Assumptions'!$B$8),'Pro Forma'!H8,0)</f>
+        <v/>
+      </c>
+      <c r="J5" s="12">
+        <f>IF(AND(J$4&gt;=1,J$4&lt;='Assumptions'!$B$8),'Pro Forma'!I8,0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="12">
+        <f>IF(AND(K$4&gt;=1,K$4&lt;='Assumptions'!$B$8),'Pro Forma'!J8,0)</f>
+        <v/>
+      </c>
+      <c r="L5" s="12">
+        <f>IF(AND(L$4&gt;=1,L$4&lt;='Assumptions'!$B$8),'Pro Forma'!K8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
           <t>Debt Service</t>
         </is>
       </c>
+      <c r="C6" s="12">
+        <f>IF(AND(C$4&gt;=1,C$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="12">
+        <f>IF(AND(D$4&gt;=1,D$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>IF(AND(E$4&gt;=1,E$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="12">
+        <f>IF(AND(F$4&gt;=1,F$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="12">
+        <f>IF(AND(G$4&gt;=1,G$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="12">
+        <f>IF(AND(H$4&gt;=1,H$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="12">
+        <f>IF(AND(I$4&gt;=1,I$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="J6" s="12">
+        <f>IF(AND(J$4&gt;=1,J$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>IF(AND(K$4&gt;=1,K$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>IF(AND(L$4&gt;=1,L$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Operating CF (levered)</t>
+        </is>
+      </c>
+      <c r="C7" s="12">
+        <f>C5+C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="12">
+        <f>D5+D6</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>E5+E6</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>F5+F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>G5+G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="12">
+        <f>H5+H6</f>
+        <v/>
+      </c>
+      <c r="I7" s="12">
+        <f>I5+I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>J5+J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="12">
+        <f>K5+K6</f>
+        <v/>
+      </c>
+      <c r="L7" s="12">
+        <f>L5+L6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Gross Sale Price (exit)</t>
+        </is>
+      </c>
+      <c r="C8" s="12">
+        <f>IF(C$4='Assumptions'!$B$8,C5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="12">
+        <f>IF(D$4='Assumptions'!$B$8,D5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="12">
+        <f>IF(E$4='Assumptions'!$B$8,E5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>IF(F$4='Assumptions'!$B$8,F5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>IF(G$4='Assumptions'!$B$8,G5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="12">
+        <f>IF(H$4='Assumptions'!$B$8,H5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="12">
+        <f>IF(I$4='Assumptions'!$B$8,I5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>IF(J$4='Assumptions'!$B$8,J5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>IF(K$4='Assumptions'!$B$8,K5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>IF(L$4='Assumptions'!$B$8,L5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Less: Selling Costs</t>
+        </is>
+      </c>
+      <c r="C9" s="12">
+        <f>-C8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="D9" s="12">
+        <f>-D8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="E9" s="12">
+        <f>-E8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="F9" s="12">
+        <f>-F8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>-G8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="H9" s="12">
+        <f>-H8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="I9" s="12">
+        <f>-I8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="J9" s="12">
+        <f>-J8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="K9" s="12">
+        <f>-K8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="L9" s="12">
+        <f>-L8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Less: Loan Payoff</t>
+        </is>
+      </c>
+      <c r="C10" s="12">
+        <f>IF(C$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="12">
+        <f>IF(D$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="E10" s="12">
+        <f>IF(E$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>IF(F$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="12">
+        <f>IF(G$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="12">
+        <f>IF(H$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="I10" s="12">
+        <f>IF(I$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="12">
+        <f>IF(J$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="12">
+        <f>IF(K$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="L10" s="12">
+        <f>IF(L$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Net Sale Proceeds</t>
+        </is>
+      </c>
       <c r="C11" s="12">
-        <f>-'Debt'!$B$9</f>
+        <f>C8+C9+C10</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>-'Debt'!$B$9</f>
+        <f>D8+D9+D10</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>-'Debt'!$B$9</f>
+        <f>E8+E9+E10</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>-'Debt'!$B$9</f>
+        <f>F8+F9+F10</f>
         <v/>
       </c>
       <c r="G11" s="12">
-        <f>-'Debt'!$B$9</f>
+        <f>G8+G9+G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="12">
+        <f>H8+H9+H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="12">
+        <f>I8+I9+I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="12">
+        <f>J8+J9+J10</f>
+        <v/>
+      </c>
+      <c r="K11" s="12">
+        <f>K8+K9+K10</f>
+        <v/>
+      </c>
+      <c r="L11" s="12">
+        <f>L8+L9+L10</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Net Levered Cash Flow</t>
         </is>
       </c>
-      <c r="B12" s="23">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="C12" s="23">
-        <f>C4+C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="23">
-        <f>D4+D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="23">
-        <f>E4+E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="23">
-        <f>F4+F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="23">
-        <f>G4+G11+G5+G6+G7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>UNLEVERED (all-cash) CASH FLOW</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="B12" s="39">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>C7+C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>D7+D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>E7+E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>F7+F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="24">
+        <f>G7+G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="24">
+        <f>H7+H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="24">
+        <f>I7+I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="24">
+        <f>J7+J11</f>
+        <v/>
+      </c>
+      <c r="K12" s="24">
+        <f>K7+K11</f>
+        <v/>
+      </c>
+      <c r="L12" s="24">
+        <f>L7+L11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Net Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B13" s="39">
+        <f>-'Sources &amp; Uses'!$B$7</f>
+        <v/>
+      </c>
+      <c r="C13" s="24">
+        <f>C5+C8+C9</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>D5+D8+D9</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>E5+E8+E9</f>
+        <v/>
+      </c>
+      <c r="F13" s="24">
+        <f>F5+F8+F9</f>
+        <v/>
+      </c>
+      <c r="G13" s="24">
+        <f>G5+G8+G9</f>
+        <v/>
+      </c>
+      <c r="H13" s="24">
+        <f>H5+H8+H9</f>
+        <v/>
+      </c>
+      <c r="I13" s="24">
+        <f>I5+I8+I9</f>
+        <v/>
+      </c>
+      <c r="J13" s="24">
+        <f>J5+J8+J9</f>
+        <v/>
+      </c>
+      <c r="K13" s="24">
+        <f>K5+K8+K9</f>
+        <v/>
+      </c>
+      <c r="L13" s="24">
+        <f>L5+L8+L9</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Initial Investment (Total Uses)</t>
-        </is>
-      </c>
-      <c r="B15" s="26">
-        <f>-'Sources &amp; Uses'!$B$7</f>
-        <v/>
-      </c>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>RETURN METRICS</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Net Unlevered Cash Flow</t>
-        </is>
-      </c>
-      <c r="B16" s="23">
-        <f>B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="23">
-        <f>C4</f>
-        <v/>
-      </c>
-      <c r="D16" s="23">
-        <f>D4</f>
-        <v/>
-      </c>
-      <c r="E16" s="23">
-        <f>E4</f>
-        <v/>
-      </c>
-      <c r="F16" s="23">
-        <f>F4</f>
-        <v/>
-      </c>
-      <c r="G16" s="23">
-        <f>G4+G5+G6</f>
-        <v/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="B16" s="40">
+        <f>IRR(B12:L12)</f>
+        <v/>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Annualized return to equity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Levered Equity Multiple</t>
+        </is>
+      </c>
+      <c r="B17" s="41">
+        <f>SUM(C12:L12)/'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Total cash returned / equity in.</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>RETURN METRICS</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Avg Cash-on-Cash (levered)</t>
+        </is>
+      </c>
+      <c r="B18" s="40">
+        <f>SUM(C7:L7)/'Assumptions'!$B$8/'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Avg annual operating CF / equity over the hold.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="34">
-        <f>IRR(B12:G12)</f>
-        <v/>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Annualized return to equity.</t>
-        </is>
+          <t>Unlevered IRR</t>
+        </is>
+      </c>
+      <c r="B19" s="40">
+        <f>IRR(B13:L13)</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Levered Equity Multiple</t>
-        </is>
-      </c>
-      <c r="B20" s="35">
-        <f>SUM(C12:G12)/'Sources &amp; Uses'!$B$11</f>
-        <v/>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Total cash returned / equity in.</t>
-        </is>
+          <t>Unlevered Equity Multiple</t>
+        </is>
+      </c>
+      <c r="B20" s="41">
+        <f>SUM(C13:L13)/'Sources &amp; Uses'!$B$7</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Avg. Cash-on-Cash (levered)</t>
-        </is>
-      </c>
-      <c r="B21" s="34">
-        <f>AVERAGE(C12:F12)/'Sources &amp; Uses'!$B$11</f>
-        <v/>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Avg annual operating CF / equity (pre-sale years).</t>
-        </is>
+          <t>Going-in Cap (as-is)</t>
+        </is>
+      </c>
+      <c r="B21" s="42">
+        <f>'Assumptions'!$B$7</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B22" s="34">
-        <f>IRR(B16:G16)</f>
+          <t>Exit Cap</t>
+        </is>
+      </c>
+      <c r="B22" s="42">
+        <f>'Assumptions'!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Going-in Cap Rate</t>
-        </is>
-      </c>
-      <c r="B23" s="34">
-        <f>'Assumptions'!$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Exit Cap Rate</t>
-        </is>
-      </c>
-      <c r="B24" s="34">
-        <f>'Assumptions'!$B$9</f>
+          <t>Hold Period (yrs)</t>
+        </is>
+      </c>
+      <c r="B23" s="22">
+        <f>'Assumptions'!$B$8</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/UW_Model_Template.xlsx
+++ b/templates/UW_Model_Template.xlsx
@@ -754,7 +754,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="25" customHeight="1">
+    <row r="14" ht="37.5" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Debt</t>
@@ -762,7 +762,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sizes &amp; amortizes the loan: annual debt service, DSCR, debt yield, and the loan payoff balance in the hold year.</t>
+          <t>Sizes the loan and supports an INTEREST-ONLY period: interest-only debt service for the first N years, then the amortizing payment. Shows both the actual Year-1 DSCR and the amortizing (stress) DSCR, debt yield, and the exit payoff balance (full loan through IO, amortizing after).</t>
         </is>
       </c>
     </row>
@@ -1381,103 +1381,103 @@
         </is>
       </c>
       <c r="B23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z23" s="12">
-        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-'Debt'!$B$9,0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(1&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)-IF(1&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(1='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^0+'Renovation'!B$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^0)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -1488,103 +1488,103 @@
         </is>
       </c>
       <c r="B24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z24" s="12">
-        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-'Debt'!$B$9,0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(2&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)-IF(2&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(2='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^1+'Renovation'!C$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^1)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -1595,103 +1595,103 @@
         </is>
       </c>
       <c r="B25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z25" s="12">
-        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-'Debt'!$B$9,0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(3&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)-IF(3&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(3='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^2+'Renovation'!D$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^2)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -1702,103 +1702,103 @@
         </is>
       </c>
       <c r="B26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z26" s="12">
-        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-'Debt'!$B$9,0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(4&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)-IF(4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(4='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^3+'Renovation'!E$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^3)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -1809,103 +1809,103 @@
         </is>
       </c>
       <c r="B27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z27" s="12">
-        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-'Debt'!$B$9,0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(5&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)-IF(5&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(5='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^4+'Renovation'!F$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^4)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -1916,103 +1916,103 @@
         </is>
       </c>
       <c r="B28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z28" s="12">
-        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-'Debt'!$B$9,0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(6&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)-IF(6&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(6='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^5+'Renovation'!G$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^5)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -2023,103 +2023,103 @@
         </is>
       </c>
       <c r="B29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z29" s="12">
-        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-'Debt'!$B$9,0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(7&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)-IF(7&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(7='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^6+'Renovation'!H$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^6)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -2130,103 +2130,103 @@
         </is>
       </c>
       <c r="B30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z30" s="12">
-        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-'Debt'!$B$9,0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(8&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)-IF(8&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(8='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^7+'Renovation'!I$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^7)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -2237,103 +2237,103 @@
         </is>
       </c>
       <c r="B31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z31" s="12">
-        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-'Debt'!$B$9,0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(9&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)-IF(9&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(9='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^8+'Renovation'!J$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^8)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -2344,103 +2344,103 @@
         </is>
       </c>
       <c r="B32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+B$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/B$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="C32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+C$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/C$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+D$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/D$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+E$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/E$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+F$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/F$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+G$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/G$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+H$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/H$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+I$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/I$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+J$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/J$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+K$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/K$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+L$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/L$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="M32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+M$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/M$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="N32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+N$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/N$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="O32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+O$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/O$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="P32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+P$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/P$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Q32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Q$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/Q$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="R32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+R$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/R$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="S32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+S$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/S$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="T32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+T$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/T$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="U32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+U$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/U$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="V32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+V$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/V$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="W32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+W$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/W$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="X32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+X$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/X$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Y32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Y$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/Y$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="Z32" s="12">
-        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-'Debt'!$B$9,0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$12,0)</f>
+        <f>IF(10&lt;='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)-IF(10&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)+IF(10='Assumptions'!$B$8,('P&amp;L'!$C$10*(1+Z$20)^9+'Renovation'!K$18-'P&amp;L'!$C$23*(1+'Assumptions'!$B$15)^9)/Z$21*(1-'Assumptions'!$B$10)-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2808,14 +2808,29 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
+          <t>Interest-Only Period (years)</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Interest-only years before amortization begins (0 = fully amortizing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>Renovation Budget (auto)</t>
         </is>
       </c>
-      <c r="B25" s="19">
+      <c r="B26" s="19">
         <f>'Renovation'!$E$9</f>
         <v/>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Totals up from the Renovation tab scope.</t>
         </is>
@@ -4623,7 +4638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4679,86 +4694,139 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Hold Period (years)</t>
+          <t>Interest-Only Period (years)</t>
         </is>
       </c>
       <c r="B7" s="11">
-        <f>'Assumptions'!$B$8</f>
-        <v/>
+        <f>'Assumptions'!$B$25</f>
+        <v/>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Interest-only years before amortization.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Monthly Payment</t>
-        </is>
-      </c>
-      <c r="B8" s="35">
+          <t>Hold Period (years)</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>'Assumptions'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Amortizing Payment</t>
+        </is>
+      </c>
+      <c r="B9" s="35">
         <f>PMT(B5/12,B6*12,-B4)</f>
         <v/>
       </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Standard amortizing payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Annual Debt Service</t>
-        </is>
-      </c>
-      <c r="B9" s="36">
-        <f>B8*12</f>
-        <v/>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Payment once amortization begins.</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>DSCR (Year-1 NOI)</t>
-        </is>
-      </c>
-      <c r="B10" s="37">
-        <f>'Pro Forma'!$B$8/B9</f>
+          <t>Annual Debt Service — Interest-Only</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>B4*B5</f>
         <v/>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>NOI / debt service. Lenders want &gt;= ~1.25x.</t>
+          <t>Years 1..IO: interest only.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Debt Yield (Year-1 NOI)</t>
-        </is>
-      </c>
-      <c r="B11" s="32">
-        <f>'Pro Forma'!$B$8/B4</f>
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Annual Debt Service — Amortizing</t>
+        </is>
+      </c>
+      <c r="B11" s="36">
+        <f>B9*12</f>
         <v/>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>NOI / loan.</t>
+          <t>After the IO period.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
+          <t>DSCR — Year 1 (actual)</t>
+        </is>
+      </c>
+      <c r="B12" s="37">
+        <f>'Pro Forma'!$B$8/IF(1&lt;=B7,B10,B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>On the actual Year-1 payment (IO if applicable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>DSCR — Amortizing (stress)</t>
+        </is>
+      </c>
+      <c r="B13" s="37">
+        <f>'Pro Forma'!$B$8/B11</f>
+        <v/>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Lender stress at the amortizing payment. Want &gt;= ~1.25x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Debt Yield (Year-1 NOI)</t>
+        </is>
+      </c>
+      <c r="B14" s="32">
+        <f>'Pro Forma'!$B$8/B4</f>
+        <v/>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>NOI / loan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
           <t>Loan Balance at Exit</t>
         </is>
       </c>
-      <c r="B12" s="12">
-        <f>B8*(1-(1+B5/12)^-(B6*12-B7*12))/(B5/12)</f>
-        <v/>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Remaining principal in the hold year.</t>
+      <c r="B15" s="12">
+        <f>IF(B8&lt;=B7,B4,B9*(1-(1+B5/12)^-(B6*12-(B8-B7)*12))/(B5/12))</f>
+        <v/>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Full loan through IO; amortizes after.</t>
         </is>
       </c>
     </row>
@@ -4956,43 +5024,43 @@
         </is>
       </c>
       <c r="C6" s="12">
-        <f>IF(AND(C$4&gt;=1,C$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(C$4&gt;=1,C$4&lt;='Assumptions'!$B$8),-IF(C$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
       <c r="D6" s="12">
-        <f>IF(AND(D$4&gt;=1,D$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(D$4&gt;=1,D$4&lt;='Assumptions'!$B$8),-IF(D$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>IF(AND(E$4&gt;=1,E$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(E$4&gt;=1,E$4&lt;='Assumptions'!$B$8),-IF(E$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IF(AND(F$4&gt;=1,F$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(F$4&gt;=1,F$4&lt;='Assumptions'!$B$8),-IF(F$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
       <c r="G6" s="12">
-        <f>IF(AND(G$4&gt;=1,G$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(G$4&gt;=1,G$4&lt;='Assumptions'!$B$8),-IF(G$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
       <c r="H6" s="12">
-        <f>IF(AND(H$4&gt;=1,H$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(H$4&gt;=1,H$4&lt;='Assumptions'!$B$8),-IF(H$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
       <c r="I6" s="12">
-        <f>IF(AND(I$4&gt;=1,I$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(I$4&gt;=1,I$4&lt;='Assumptions'!$B$8),-IF(I$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
       <c r="J6" s="12">
-        <f>IF(AND(J$4&gt;=1,J$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(J$4&gt;=1,J$4&lt;='Assumptions'!$B$8),-IF(J$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
       <c r="K6" s="12">
-        <f>IF(AND(K$4&gt;=1,K$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(K$4&gt;=1,K$4&lt;='Assumptions'!$B$8),-IF(K$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
       <c r="L6" s="12">
-        <f>IF(AND(L$4&gt;=1,L$4&lt;='Assumptions'!$B$8),-'Debt'!$B$9,0)</f>
+        <f>IF(AND(L$4&gt;=1,L$4&lt;='Assumptions'!$B$8),-IF(L$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
         <v/>
       </c>
     </row>
@@ -5144,43 +5212,43 @@
         </is>
       </c>
       <c r="C10" s="12">
-        <f>IF(C$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(C$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="D10" s="12">
-        <f>IF(D$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(D$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>IF(E$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(E$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IF(F$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(F$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="G10" s="12">
-        <f>IF(G$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(G$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="H10" s="12">
-        <f>IF(H$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(H$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="I10" s="12">
-        <f>IF(I$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(I$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="J10" s="12">
-        <f>IF(J$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(J$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="K10" s="12">
-        <f>IF(K$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(K$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
       <c r="L10" s="12">
-        <f>IF(L$4='Assumptions'!$B$8,-'Debt'!$B$12,0)</f>
+        <f>IF(L$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
         <v/>
       </c>
     </row>

--- a/templates/UW_Model_Template.xlsx
+++ b/templates/UW_Model_Template.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="RR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Renovation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="P&amp;L" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Pro Forma" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sources &amp; Uses" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Debt" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Returns" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Sensitivity" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Rent Roll (Input)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="RR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Renovation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="P&amp;L" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pro Forma" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sources &amp; Uses" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Debt" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Returns" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Sensitivity" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,11 +26,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -181,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -212,12 +214,18 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -226,24 +234,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -624,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -658,7 +662,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="25" customHeight="1">
+    <row r="5" ht="37.5" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Fill order</t>
@@ -666,7 +670,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1) Assumptions  2) RR (rent roll)  3) Renovation (value-add scope &amp; timing)  4) P&amp;L (enter in-place expenses)  5) review Pro Forma / Debt / Returns / Sensitivity (all auto-calc).</t>
+          <t>1) Assumptions  2) Rent Roll (Input) — paste the property's unit-level rent roll  3) RR — list each floor plan  4) Renovation (value-add scope &amp; timing)  5) P&amp;L (enter in-place expenses)  6) review Pro Forma / Debt / Returns / Sensitivity (all auto-calc).</t>
         </is>
       </c>
     </row>
@@ -694,141 +698,153 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="25" customHeight="1">
+    <row r="9" ht="37.5" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>RR  (Rent Roll)</t>
+          <t>Rent Roll (Input)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Unit-level income engine. Unit mix x in-place rent = in-place GPR; unit mix x market rent = as-is market GPR. Feeds the P&amp;L top line and the unit count.</t>
+          <t>Paste ANY property's rent roll here — one row per unit (unit #, floor plan, SF, status, in-place rent, market rent, lease dates). Nothing to calculate; it is the raw data source. The Floor-Plan text is the key the RR tab groups on.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="62.5" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>RR  (unit-mix rollup)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Auto-aggregates the Rent Roll (Input) tab by floor plan (COUNTIF / SUMIFS / AVERAGEIFS): # units, avg SF, avg in-place &amp; market rent, and in-place vs. market GPR. You only type each distinct floor-plan NAME in column A (matching the input tab); the rest is computed. Feeds the P&amp;L top line and the unit count. A check row flags any floor plan in the rent roll that you haven't listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62.5" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>Renovation  (value-add)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>The value-add engine. Per unit type: how many units you renovate, the cost/unit, and the rent premium/unit achieved ABOVE market. Sums to a total renovation budget (-&gt; Sources &amp; Uses) and a rent-premium schedule phased by your completion %/year (-&gt; Pro Forma). Capex is funded upfront in the capital stack; the timing row shows when the budget is drawn and when the premium is earned.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="37.5" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12" ht="37.5" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>P&amp;L  (Operating Statement)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Turns rent into cash flow. GPR (from RR) - vacancy &amp; bad debt + other income = EGI; EGI - operating expenses = NOI. Two columns: In-Place (T-12 you type) and Year-1 Underwritten (as-is market). NOI is the single most important number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Pro Forma (10-yr)</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Projects Year-1 underwritten EGI &amp; OpEx across up to 10 years using the growth rates, then LAYERS ON the renovation premium schedule -&gt; NOI each year.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Pro Forma (10-yr)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Projects Year-1 underwritten EGI &amp; OpEx across up to 10 years using the growth rates, then LAYERS ON the renovation premium schedule -&gt; NOI each year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>Sources &amp; Uses</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Capital stack. Uses = price + closing + renovation budget (from Renovation). Sources = senior loan (LTV x price) + equity (the plug). Equity anchors returns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="37.5" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Debt</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Sizes the loan and supports an INTEREST-ONLY period: interest-only debt service for the first N years, then the amortizing payment. Shows both the actual Year-1 DSCR and the amortizing (stress) DSCR, debt yield, and the exit payoff balance (full loan through IO, amortizing after).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="37.5" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Returns</t>
+          <t>Debt</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Ties it together, exiting in your chosen hold year: levered CF = Pro Forma NOI - debt service; exit value = hold-year NOI / exit cap; proceeds repay the loan -&gt; IRR, equity multiple, cash-on-cash (levered &amp; unlevered).</t>
+          <t>Sizes the loan and supports an INTEREST-ONLY period: interest-only debt service for the first N years, then the amortizing payment. Shows both the actual Year-1 DSCR and the amortizing (stress) DSCR, debt yield, and the exit payoff balance (full loan through IO, amortizing after).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="37.5" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Returns</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Ties it together, exiting in your chosen hold year: levered CF = Pro Forma NOI - debt service; exit value = hold-year NOI / exit cap; proceeds repay the loan -&gt; IRR, equity multiple, cash-on-cash (levered &amp; unlevered).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="37.5" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Sensitivity</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>A 2-way grid of levered IRR across Exit Cap (columns) x Rent Growth (rows). It re-runs the full levered cash flow for each combination via backing calcs below the grid, so it updates live when you change the deal. The center cell equals the Returns tab IRR.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="37.5" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="37.5" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>One sentence</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>RR + Renovation build income -&gt; P&amp;L converts it to NOI -&gt; Pro Forma grows &amp; renovates NOI over the hold -&gt; Sources &amp; Uses and Debt set the capital -&gt; Returns measures the equity's IRR -&gt; Sensitivity stress-tests it.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="37.5" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="37.5" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Renovation funding note</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>The renovation budget is included in Uses and funded at close (equity + loan), so it is NOT subtracted again from operating cash flow. The Renovation timing row is informational (draw schedule) and drives WHEN the rent premium is realized.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Teaching/starter template with illustrative numbers (a ~100-unit value-add deal). Replace every blue/yellow cell with your deal's data. Not investment advice.</t>
         </is>
@@ -843,6 +859,698 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Returns  —  levered &amp; unlevered (exits in the hold year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Year 0</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>Year 6</t>
+        </is>
+      </c>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>Year 7</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>Year 8</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>Year 9</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t>Year 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Year #</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" s="41" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>NOI (from Pro Forma)</t>
+        </is>
+      </c>
+      <c r="C5" s="12">
+        <f>IF(AND(C$4&gt;=1,C$4&lt;='Assumptions'!$B$8),'Pro Forma'!B8,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="12">
+        <f>IF(AND(D$4&gt;=1,D$4&lt;='Assumptions'!$B$8),'Pro Forma'!C8,0)</f>
+        <v/>
+      </c>
+      <c r="E5" s="12">
+        <f>IF(AND(E$4&gt;=1,E$4&lt;='Assumptions'!$B$8),'Pro Forma'!D8,0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="12">
+        <f>IF(AND(F$4&gt;=1,F$4&lt;='Assumptions'!$B$8),'Pro Forma'!E8,0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>IF(AND(G$4&gt;=1,G$4&lt;='Assumptions'!$B$8),'Pro Forma'!F8,0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="12">
+        <f>IF(AND(H$4&gt;=1,H$4&lt;='Assumptions'!$B$8),'Pro Forma'!G8,0)</f>
+        <v/>
+      </c>
+      <c r="I5" s="12">
+        <f>IF(AND(I$4&gt;=1,I$4&lt;='Assumptions'!$B$8),'Pro Forma'!H8,0)</f>
+        <v/>
+      </c>
+      <c r="J5" s="12">
+        <f>IF(AND(J$4&gt;=1,J$4&lt;='Assumptions'!$B$8),'Pro Forma'!I8,0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="12">
+        <f>IF(AND(K$4&gt;=1,K$4&lt;='Assumptions'!$B$8),'Pro Forma'!J8,0)</f>
+        <v/>
+      </c>
+      <c r="L5" s="12">
+        <f>IF(AND(L$4&gt;=1,L$4&lt;='Assumptions'!$B$8),'Pro Forma'!K8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Debt Service</t>
+        </is>
+      </c>
+      <c r="C6" s="12">
+        <f>IF(AND(C$4&gt;=1,C$4&lt;='Assumptions'!$B$8),-IF(C$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="12">
+        <f>IF(AND(D$4&gt;=1,D$4&lt;='Assumptions'!$B$8),-IF(D$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>IF(AND(E$4&gt;=1,E$4&lt;='Assumptions'!$B$8),-IF(E$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="12">
+        <f>IF(AND(F$4&gt;=1,F$4&lt;='Assumptions'!$B$8),-IF(F$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="12">
+        <f>IF(AND(G$4&gt;=1,G$4&lt;='Assumptions'!$B$8),-IF(G$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="12">
+        <f>IF(AND(H$4&gt;=1,H$4&lt;='Assumptions'!$B$8),-IF(H$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="12">
+        <f>IF(AND(I$4&gt;=1,I$4&lt;='Assumptions'!$B$8),-IF(I$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="J6" s="12">
+        <f>IF(AND(J$4&gt;=1,J$4&lt;='Assumptions'!$B$8),-IF(J$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>IF(AND(K$4&gt;=1,K$4&lt;='Assumptions'!$B$8),-IF(K$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>IF(AND(L$4&gt;=1,L$4&lt;='Assumptions'!$B$8),-IF(L$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Operating CF (levered)</t>
+        </is>
+      </c>
+      <c r="C7" s="12">
+        <f>C5+C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="12">
+        <f>D5+D6</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>E5+E6</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>F5+F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>G5+G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="12">
+        <f>H5+H6</f>
+        <v/>
+      </c>
+      <c r="I7" s="12">
+        <f>I5+I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>J5+J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="12">
+        <f>K5+K6</f>
+        <v/>
+      </c>
+      <c r="L7" s="12">
+        <f>L5+L6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Gross Sale Price (exit)</t>
+        </is>
+      </c>
+      <c r="C8" s="12">
+        <f>IF(C$4='Assumptions'!$B$8,C5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="12">
+        <f>IF(D$4='Assumptions'!$B$8,D5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="12">
+        <f>IF(E$4='Assumptions'!$B$8,E5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>IF(F$4='Assumptions'!$B$8,F5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>IF(G$4='Assumptions'!$B$8,G5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="12">
+        <f>IF(H$4='Assumptions'!$B$8,H5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="12">
+        <f>IF(I$4='Assumptions'!$B$8,I5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>IF(J$4='Assumptions'!$B$8,J5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>IF(K$4='Assumptions'!$B$8,K5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>IF(L$4='Assumptions'!$B$8,L5/'Assumptions'!$B$9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Less: Selling Costs</t>
+        </is>
+      </c>
+      <c r="C9" s="12">
+        <f>-C8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="D9" s="12">
+        <f>-D8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="E9" s="12">
+        <f>-E8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="F9" s="12">
+        <f>-F8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>-G8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="H9" s="12">
+        <f>-H8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="I9" s="12">
+        <f>-I8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="J9" s="12">
+        <f>-J8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="K9" s="12">
+        <f>-K8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+      <c r="L9" s="12">
+        <f>-L8*'Assumptions'!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Less: Loan Payoff</t>
+        </is>
+      </c>
+      <c r="C10" s="12">
+        <f>IF(C$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="12">
+        <f>IF(D$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="E10" s="12">
+        <f>IF(E$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>IF(F$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="12">
+        <f>IF(G$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="12">
+        <f>IF(H$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="I10" s="12">
+        <f>IF(I$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="12">
+        <f>IF(J$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="12">
+        <f>IF(K$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="L10" s="12">
+        <f>IF(L$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Net Sale Proceeds</t>
+        </is>
+      </c>
+      <c r="C11" s="12">
+        <f>C8+C9+C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="12">
+        <f>D8+D9+D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="12">
+        <f>E8+E9+E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="12">
+        <f>F8+F9+F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="12">
+        <f>G8+G9+G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="12">
+        <f>H8+H9+H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="12">
+        <f>I8+I9+I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="12">
+        <f>J8+J9+J10</f>
+        <v/>
+      </c>
+      <c r="K11" s="12">
+        <f>K8+K9+K10</f>
+        <v/>
+      </c>
+      <c r="L11" s="12">
+        <f>L8+L9+L10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Net Levered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B12" s="42">
+        <f>-'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="C12" s="28">
+        <f>C7+C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="28">
+        <f>D7+D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="28">
+        <f>E7+E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="28">
+        <f>F7+F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="28">
+        <f>G7+G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="28">
+        <f>H7+H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="28">
+        <f>I7+I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="28">
+        <f>J7+J11</f>
+        <v/>
+      </c>
+      <c r="K12" s="28">
+        <f>K7+K11</f>
+        <v/>
+      </c>
+      <c r="L12" s="28">
+        <f>L7+L11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Net Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B13" s="42">
+        <f>-'Sources &amp; Uses'!$B$7</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>C5+C8+C9</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>D5+D8+D9</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>E5+E8+E9</f>
+        <v/>
+      </c>
+      <c r="F13" s="28">
+        <f>F5+F8+F9</f>
+        <v/>
+      </c>
+      <c r="G13" s="28">
+        <f>G5+G8+G9</f>
+        <v/>
+      </c>
+      <c r="H13" s="28">
+        <f>H5+H8+H9</f>
+        <v/>
+      </c>
+      <c r="I13" s="28">
+        <f>I5+I8+I9</f>
+        <v/>
+      </c>
+      <c r="J13" s="28">
+        <f>J5+J8+J9</f>
+        <v/>
+      </c>
+      <c r="K13" s="28">
+        <f>K5+K8+K9</f>
+        <v/>
+      </c>
+      <c r="L13" s="28">
+        <f>L5+L8+L9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>RETURN METRICS</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="B16" s="25">
+        <f>IRR(B12:L12)</f>
+        <v/>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Annualized return to equity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Levered Equity Multiple</t>
+        </is>
+      </c>
+      <c r="B17" s="43">
+        <f>SUM(C12:L12)/'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Total cash returned / equity in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Avg Cash-on-Cash (levered)</t>
+        </is>
+      </c>
+      <c r="B18" s="25">
+        <f>SUM(C7:L7)/'Assumptions'!$B$8/'Sources &amp; Uses'!$B$11</f>
+        <v/>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Avg annual operating CF / equity over the hold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Unlevered IRR</t>
+        </is>
+      </c>
+      <c r="B19" s="25">
+        <f>IRR(B13:L13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Unlevered Equity Multiple</t>
+        </is>
+      </c>
+      <c r="B20" s="43">
+        <f>SUM(C13:L13)/'Sources &amp; Uses'!$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Going-in Cap (as-is)</t>
+        </is>
+      </c>
+      <c r="B21" s="44">
+        <f>'Assumptions'!$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Exit Cap</t>
+        </is>
+      </c>
+      <c r="B22" s="44">
+        <f>'Assumptions'!$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Hold Period (yrs)</t>
+        </is>
+      </c>
+      <c r="B23" s="24">
+        <f>'Assumptions'!$B$8</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -868,148 +1576,148 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>Growth \ Exit Cap</t>
         </is>
       </c>
-      <c r="C5" s="44" t="n">
+      <c r="C5" s="46" t="n">
         <v>0.05</v>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="46" t="n">
         <v>0.055</v>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="46" t="n">
         <v>0.06</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="46" t="n">
         <v>0.065</v>
       </c>
-      <c r="G5" s="44" t="n">
+      <c r="G5" s="46" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="47" t="n">
         <v>0.01</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="48">
         <f>B$33</f>
         <v/>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="48">
         <f>C$33</f>
         <v/>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="48">
         <f>D$33</f>
         <v/>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="48">
         <f>E$33</f>
         <v/>
       </c>
-      <c r="G6" s="46">
+      <c r="G6" s="48">
         <f>F$33</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="47" t="n">
         <v>0.02</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="48">
         <f>G$33</f>
         <v/>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="48">
         <f>H$33</f>
         <v/>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="48">
         <f>I$33</f>
         <v/>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="48">
         <f>J$33</f>
         <v/>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="48">
         <f>K$33</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="47" t="n">
         <v>0.03</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="48">
         <f>L$33</f>
         <v/>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="48">
         <f>M$33</f>
         <v/>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="49">
         <f>N$33</f>
         <v/>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="48">
         <f>O$33</f>
         <v/>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="48">
         <f>P$33</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="47" t="n">
         <v>0.04</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="48">
         <f>Q$33</f>
         <v/>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="48">
         <f>R$33</f>
         <v/>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="48">
         <f>S$33</f>
         <v/>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="48">
         <f>T$33</f>
         <v/>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="48">
         <f>U$33</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="47" t="n">
         <v>0.05</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="48">
         <f>V$33</f>
         <v/>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="48">
         <f>W$33</f>
         <v/>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="48">
         <f>X$33</f>
         <v/>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="48">
         <f>Y$33</f>
         <v/>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="48">
         <f>Z$33</f>
         <v/>
       </c>
@@ -1054,7 +1762,7 @@
       <c r="Z19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Rent Growth (g)</t>
         </is>
@@ -1161,7 +1869,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Exit Cap (X)</t>
         </is>
@@ -1268,7 +1976,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>CF Year 0</t>
         </is>
@@ -1375,7 +2083,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>CF Year 1</t>
         </is>
@@ -1482,7 +2190,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>CF Year 2</t>
         </is>
@@ -1589,7 +2297,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>CF Year 3</t>
         </is>
@@ -1696,7 +2404,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>CF Year 4</t>
         </is>
@@ -1803,7 +2511,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>CF Year 5</t>
         </is>
@@ -1910,7 +2618,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>CF Year 6</t>
         </is>
@@ -2017,7 +2725,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>CF Year 7</t>
         </is>
@@ -2124,7 +2832,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>CF Year 8</t>
         </is>
@@ -2231,7 +2939,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>CF Year 9</t>
         </is>
@@ -2338,7 +3046,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>CF Year 10</t>
         </is>
@@ -2445,108 +3153,108 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>Levered IRR</t>
         </is>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="35">
         <f>IRR(B22:B32)</f>
         <v/>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="35">
         <f>IRR(C22:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="35">
         <f>IRR(D22:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="35">
         <f>IRR(E22:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="35">
         <f>IRR(F22:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="35">
         <f>IRR(G22:G32)</f>
         <v/>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="35">
         <f>IRR(H22:H32)</f>
         <v/>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="35">
         <f>IRR(I22:I32)</f>
         <v/>
       </c>
-      <c r="J33" s="32">
+      <c r="J33" s="35">
         <f>IRR(J22:J32)</f>
         <v/>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="35">
         <f>IRR(K22:K32)</f>
         <v/>
       </c>
-      <c r="L33" s="32">
+      <c r="L33" s="35">
         <f>IRR(L22:L32)</f>
         <v/>
       </c>
-      <c r="M33" s="32">
+      <c r="M33" s="35">
         <f>IRR(M22:M32)</f>
         <v/>
       </c>
-      <c r="N33" s="32">
+      <c r="N33" s="35">
         <f>IRR(N22:N32)</f>
         <v/>
       </c>
-      <c r="O33" s="32">
+      <c r="O33" s="35">
         <f>IRR(O22:O32)</f>
         <v/>
       </c>
-      <c r="P33" s="32">
+      <c r="P33" s="35">
         <f>IRR(P22:P32)</f>
         <v/>
       </c>
-      <c r="Q33" s="32">
+      <c r="Q33" s="35">
         <f>IRR(Q22:Q32)</f>
         <v/>
       </c>
-      <c r="R33" s="32">
+      <c r="R33" s="35">
         <f>IRR(R22:R32)</f>
         <v/>
       </c>
-      <c r="S33" s="32">
+      <c r="S33" s="35">
         <f>IRR(S22:S32)</f>
         <v/>
       </c>
-      <c r="T33" s="32">
+      <c r="T33" s="35">
         <f>IRR(T22:T32)</f>
         <v/>
       </c>
-      <c r="U33" s="32">
+      <c r="U33" s="35">
         <f>IRR(U22:U32)</f>
         <v/>
       </c>
-      <c r="V33" s="32">
+      <c r="V33" s="35">
         <f>IRR(V22:V32)</f>
         <v/>
       </c>
-      <c r="W33" s="32">
+      <c r="W33" s="35">
         <f>IRR(W22:W32)</f>
         <v/>
       </c>
-      <c r="X33" s="32">
+      <c r="X33" s="35">
         <f>IRR(X22:X32)</f>
         <v/>
       </c>
-      <c r="Y33" s="32">
+      <c r="Y33" s="35">
         <f>IRR(Y22:Y32)</f>
         <v/>
       </c>
-      <c r="Z33" s="32">
+      <c r="Z33" s="35">
         <f>IRR(Z22:Z32)</f>
         <v/>
       </c>
@@ -2611,7 +3319,7 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>'RR'!$B$8</f>
+        <f>'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -2850,10 +3558,3490 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rent Roll (Input)  —  paste ANY property's rent roll (one row per unit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>One row per unit. The RR tab groups these by the Floor-Plan text, so the floor-plan names here must match the unit-type names on the RR tab exactly. Blue cells are yours — clear the sample rows and paste your property. Status uses the dropdown (Occupied / Vacant / Model / Down / Notice).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Unit / Apt #</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Floor Plan (Unit Type)</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Beds</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Baths</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>In-Place Rent
+($/mo)</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Market/Asking
+Rent ($/mo)</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Lease Start</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>Lease End</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="n">
+        <v>101</v>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I5" s="23" t="n"/>
+      <c r="J5" s="23" t="n"/>
+      <c r="K5" s="22" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>102</v>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="22" t="n"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="n">
+        <v>103</v>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I7" s="23" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Total Units (rows)</t>
+        </is>
+      </c>
+      <c r="N7" s="24">
+        <f>COUNTA($A$5:$A$504)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="n">
+        <v>104</v>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="22" t="n"/>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="N8" s="24">
+        <f>COUNTIF($F$5:$F$504,"Occupied")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>105</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="22" t="n"/>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>Vacant</t>
+        </is>
+      </c>
+      <c r="N9" s="24">
+        <f>COUNTIF($F$5:$F$504,"Vacant")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>106</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>Occupancy %</t>
+        </is>
+      </c>
+      <c r="N10" s="25">
+        <f>IFERROR(N8/N7,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>107</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>In-Place Rent ($/yr, occ)</t>
+        </is>
+      </c>
+      <c r="N11" s="26">
+        <f>SUMIFS($G$5:$G$504,$F$5:$F$504,"Occupied")*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>108</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Market GPR ($/yr)</t>
+        </is>
+      </c>
+      <c r="N12" s="26">
+        <f>SUM($H$5:$H$504)*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>109</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I13" s="23" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>Avg In-Place (occ, $/mo)</t>
+        </is>
+      </c>
+      <c r="N13" s="26">
+        <f>IFERROR(N11/12/N8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>110</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I14" s="23" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="22" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>111</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="22" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>112</v>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I16" s="23" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="22" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>113</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I17" s="23" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="22" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>114</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I18" s="23" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="22" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>115</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I19" s="23" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="22" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>116</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I20" s="23" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="22" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>117</v>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="22" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="n">
+        <v>118</v>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="22" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="n">
+        <v>119</v>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I23" s="23" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="22" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="n">
+        <v>120</v>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I24" s="23" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="22" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n">
+        <v>121</v>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="22" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="n">
+        <v>122</v>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="22" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>123</v>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I27" s="23" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="22" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>124</v>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I28" s="23" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="22" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="n">
+        <v>125</v>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I29" s="23" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="22" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="22" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="n">
+        <v>127</v>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I31" s="23" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="22" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n">
+        <v>128</v>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I32" s="23" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="22" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="n">
+        <v>129</v>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I33" s="23" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="22" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n">
+        <v>130</v>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I34" s="23" t="n"/>
+      <c r="J34" s="23" t="n"/>
+      <c r="K34" s="22" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="n">
+        <v>131</v>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I35" s="23" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="22" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="n">
+        <v>132</v>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I36" s="23" t="n"/>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="22" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="n">
+        <v>133</v>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I37" s="23" t="n"/>
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="22" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="n">
+        <v>134</v>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I38" s="23" t="n"/>
+      <c r="J38" s="23" t="n"/>
+      <c r="K38" s="22" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="n">
+        <v>135</v>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I39" s="23" t="n"/>
+      <c r="J39" s="23" t="n"/>
+      <c r="K39" s="22" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n">
+        <v>136</v>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I40" s="23" t="n"/>
+      <c r="J40" s="23" t="n"/>
+      <c r="K40" s="22" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>137</v>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I41" s="23" t="n"/>
+      <c r="J41" s="23" t="n"/>
+      <c r="K41" s="22" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n">
+        <v>138</v>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I42" s="23" t="n"/>
+      <c r="J42" s="23" t="n"/>
+      <c r="K42" s="22" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="n">
+        <v>139</v>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I43" s="23" t="n"/>
+      <c r="J43" s="23" t="n"/>
+      <c r="K43" s="22" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="n">
+        <v>140</v>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>1 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I44" s="23" t="n"/>
+      <c r="J44" s="23" t="n"/>
+      <c r="K44" s="22" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="n">
+        <v>201</v>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I45" s="23" t="n"/>
+      <c r="J45" s="23" t="n"/>
+      <c r="K45" s="22" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="n">
+        <v>202</v>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I46" s="23" t="n"/>
+      <c r="J46" s="23" t="n"/>
+      <c r="K46" s="22" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="n">
+        <v>203</v>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I47" s="23" t="n"/>
+      <c r="J47" s="23" t="n"/>
+      <c r="K47" s="22" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="n">
+        <v>204</v>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H48" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I48" s="23" t="n"/>
+      <c r="J48" s="23" t="n"/>
+      <c r="K48" s="22" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="n">
+        <v>205</v>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I49" s="23" t="n"/>
+      <c r="J49" s="23" t="n"/>
+      <c r="K49" s="22" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="n">
+        <v>206</v>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I50" s="23" t="n"/>
+      <c r="J50" s="23" t="n"/>
+      <c r="K50" s="22" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="n">
+        <v>207</v>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H51" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I51" s="23" t="n"/>
+      <c r="J51" s="23" t="n"/>
+      <c r="K51" s="22" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="n">
+        <v>208</v>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H52" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I52" s="23" t="n"/>
+      <c r="J52" s="23" t="n"/>
+      <c r="K52" s="22" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="n">
+        <v>209</v>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H53" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I53" s="23" t="n"/>
+      <c r="J53" s="23" t="n"/>
+      <c r="K53" s="22" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="n">
+        <v>210</v>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I54" s="23" t="n"/>
+      <c r="J54" s="23" t="n"/>
+      <c r="K54" s="22" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="n">
+        <v>211</v>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H55" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I55" s="23" t="n"/>
+      <c r="J55" s="23" t="n"/>
+      <c r="K55" s="22" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="n">
+        <v>212</v>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I56" s="23" t="n"/>
+      <c r="J56" s="23" t="n"/>
+      <c r="K56" s="22" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="n">
+        <v>213</v>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H57" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I57" s="23" t="n"/>
+      <c r="J57" s="23" t="n"/>
+      <c r="K57" s="22" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="n">
+        <v>214</v>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H58" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I58" s="23" t="n"/>
+      <c r="J58" s="23" t="n"/>
+      <c r="K58" s="22" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="n">
+        <v>215</v>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H59" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I59" s="23" t="n"/>
+      <c r="J59" s="23" t="n"/>
+      <c r="K59" s="22" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="n">
+        <v>216</v>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H60" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I60" s="23" t="n"/>
+      <c r="J60" s="23" t="n"/>
+      <c r="K60" s="22" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="n">
+        <v>217</v>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H61" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I61" s="23" t="n"/>
+      <c r="J61" s="23" t="n"/>
+      <c r="K61" s="22" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="n">
+        <v>218</v>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F62" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H62" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I62" s="23" t="n"/>
+      <c r="J62" s="23" t="n"/>
+      <c r="K62" s="22" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="n">
+        <v>219</v>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H63" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I63" s="23" t="n"/>
+      <c r="J63" s="23" t="n"/>
+      <c r="K63" s="22" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="n">
+        <v>220</v>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H64" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I64" s="23" t="n"/>
+      <c r="J64" s="23" t="n"/>
+      <c r="K64" s="22" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="n">
+        <v>221</v>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H65" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I65" s="23" t="n"/>
+      <c r="J65" s="23" t="n"/>
+      <c r="K65" s="22" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="n">
+        <v>222</v>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H66" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I66" s="23" t="n"/>
+      <c r="J66" s="23" t="n"/>
+      <c r="K66" s="22" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="n">
+        <v>223</v>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H67" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I67" s="23" t="n"/>
+      <c r="J67" s="23" t="n"/>
+      <c r="K67" s="22" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="n">
+        <v>224</v>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H68" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I68" s="23" t="n"/>
+      <c r="J68" s="23" t="n"/>
+      <c r="K68" s="22" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="n">
+        <v>225</v>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F69" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H69" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I69" s="23" t="n"/>
+      <c r="J69" s="23" t="n"/>
+      <c r="K69" s="22" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="n">
+        <v>226</v>
+      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F70" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H70" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I70" s="23" t="n"/>
+      <c r="J70" s="23" t="n"/>
+      <c r="K70" s="22" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="n">
+        <v>227</v>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F71" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H71" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I71" s="23" t="n"/>
+      <c r="J71" s="23" t="n"/>
+      <c r="K71" s="22" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="n">
+        <v>228</v>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F72" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H72" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I72" s="23" t="n"/>
+      <c r="J72" s="23" t="n"/>
+      <c r="K72" s="22" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="n">
+        <v>229</v>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F73" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H73" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I73" s="23" t="n"/>
+      <c r="J73" s="23" t="n"/>
+      <c r="K73" s="22" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="n">
+        <v>230</v>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 1 BA</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="F74" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H74" s="17" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I74" s="23" t="n"/>
+      <c r="J74" s="23" t="n"/>
+      <c r="K74" s="22" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="n">
+        <v>231</v>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F75" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H75" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I75" s="23" t="n"/>
+      <c r="J75" s="23" t="n"/>
+      <c r="K75" s="22" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="n">
+        <v>232</v>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F76" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H76" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I76" s="23" t="n"/>
+      <c r="J76" s="23" t="n"/>
+      <c r="K76" s="22" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="22" t="n">
+        <v>233</v>
+      </c>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F77" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H77" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I77" s="23" t="n"/>
+      <c r="J77" s="23" t="n"/>
+      <c r="K77" s="22" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="n">
+        <v>234</v>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F78" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H78" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I78" s="23" t="n"/>
+      <c r="J78" s="23" t="n"/>
+      <c r="K78" s="22" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="22" t="n">
+        <v>235</v>
+      </c>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F79" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H79" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I79" s="23" t="n"/>
+      <c r="J79" s="23" t="n"/>
+      <c r="K79" s="22" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="n">
+        <v>236</v>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F80" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H80" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I80" s="23" t="n"/>
+      <c r="J80" s="23" t="n"/>
+      <c r="K80" s="22" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="n">
+        <v>237</v>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F81" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H81" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I81" s="23" t="n"/>
+      <c r="J81" s="23" t="n"/>
+      <c r="K81" s="22" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="n">
+        <v>238</v>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F82" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H82" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I82" s="23" t="n"/>
+      <c r="J82" s="23" t="n"/>
+      <c r="K82" s="22" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="22" t="n">
+        <v>239</v>
+      </c>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F83" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H83" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I83" s="23" t="n"/>
+      <c r="J83" s="23" t="n"/>
+      <c r="K83" s="22" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="n">
+        <v>240</v>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F84" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H84" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I84" s="23" t="n"/>
+      <c r="J84" s="23" t="n"/>
+      <c r="K84" s="22" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="n">
+        <v>241</v>
+      </c>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F85" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H85" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I85" s="23" t="n"/>
+      <c r="J85" s="23" t="n"/>
+      <c r="K85" s="22" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="n">
+        <v>242</v>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F86" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H86" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I86" s="23" t="n"/>
+      <c r="J86" s="23" t="n"/>
+      <c r="K86" s="22" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="22" t="n">
+        <v>243</v>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F87" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G87" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H87" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I87" s="23" t="n"/>
+      <c r="J87" s="23" t="n"/>
+      <c r="K87" s="22" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="n">
+        <v>244</v>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F88" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H88" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I88" s="23" t="n"/>
+      <c r="J88" s="23" t="n"/>
+      <c r="K88" s="22" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="22" t="n">
+        <v>245</v>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F89" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H89" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I89" s="23" t="n"/>
+      <c r="J89" s="23" t="n"/>
+      <c r="K89" s="22" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="n">
+        <v>246</v>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F90" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H90" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I90" s="23" t="n"/>
+      <c r="J90" s="23" t="n"/>
+      <c r="K90" s="22" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="n">
+        <v>247</v>
+      </c>
+      <c r="B91" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F91" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G91" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H91" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I91" s="23" t="n"/>
+      <c r="J91" s="23" t="n"/>
+      <c r="K91" s="22" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="n">
+        <v>248</v>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F92" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H92" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I92" s="23" t="n"/>
+      <c r="J92" s="23" t="n"/>
+      <c r="K92" s="22" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="n">
+        <v>249</v>
+      </c>
+      <c r="B93" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F93" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H93" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I93" s="23" t="n"/>
+      <c r="J93" s="23" t="n"/>
+      <c r="K93" s="22" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="n">
+        <v>250</v>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>2 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F94" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H94" s="17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I94" s="23" t="n"/>
+      <c r="J94" s="23" t="n"/>
+      <c r="K94" s="22" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="22" t="n">
+        <v>301</v>
+      </c>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F95" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G95" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H95" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I95" s="23" t="n"/>
+      <c r="J95" s="23" t="n"/>
+      <c r="K95" s="22" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="22" t="n">
+        <v>302</v>
+      </c>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F96" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H96" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I96" s="23" t="n"/>
+      <c r="J96" s="23" t="n"/>
+      <c r="K96" s="22" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="22" t="n">
+        <v>303</v>
+      </c>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F97" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G97" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H97" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I97" s="23" t="n"/>
+      <c r="J97" s="23" t="n"/>
+      <c r="K97" s="22" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="22" t="n">
+        <v>304</v>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D98" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F98" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H98" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I98" s="23" t="n"/>
+      <c r="J98" s="23" t="n"/>
+      <c r="K98" s="22" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="22" t="n">
+        <v>305</v>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F99" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G99" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H99" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I99" s="23" t="n"/>
+      <c r="J99" s="23" t="n"/>
+      <c r="K99" s="22" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="22" t="n">
+        <v>306</v>
+      </c>
+      <c r="B100" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F100" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H100" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I100" s="23" t="n"/>
+      <c r="J100" s="23" t="n"/>
+      <c r="K100" s="22" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="22" t="n">
+        <v>307</v>
+      </c>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F101" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G101" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H101" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I101" s="23" t="n"/>
+      <c r="J101" s="23" t="n"/>
+      <c r="K101" s="22" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="22" t="n">
+        <v>308</v>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D102" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F102" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H102" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I102" s="23" t="n"/>
+      <c r="J102" s="23" t="n"/>
+      <c r="K102" s="22" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="22" t="n">
+        <v>309</v>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F103" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G103" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H103" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I103" s="23" t="n"/>
+      <c r="J103" s="23" t="n"/>
+      <c r="K103" s="22" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="22" t="n">
+        <v>310</v>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>3 BD / 2 BA</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F104" s="22" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="G104" s="17" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H104" s="17" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I104" s="23" t="n"/>
+      <c r="J104" s="23" t="n"/>
+      <c r="K104" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Occupied,Vacant,Model,Down,Notice"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2867,57 +7055,64 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RR  —  Rent Roll  (unit-level income engine)</t>
+          <t>RR  —  Rent Roll Unit-Mix Summary  (auto from Rent Roll (Input))</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Type each distinct FLOOR PLAN in column A (matching the Rent Roll (Input) tab). Columns B-I auto-aggregate from the input tab — green cells are pulled from it. Add rows in col A as needed (up to 12 plans).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>Unit Type</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Floor Plan (Unit Type)</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t># Units</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>Avg SF</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>In-Place Rent
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Avg In-Place
 ($/unit/mo)</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>Market Rent
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Avg Market
 ($/unit/mo)</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>In-Place
 Monthly</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t>In-Place
 Annual</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>Market
 Monthly</t>
         </is>
       </c>
-      <c r="I3" s="20" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t>Market
 Annual</t>
@@ -2925,33 +7120,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>1 BD / 1 BA</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="C4" s="18" t="n">
-        <v>700</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>1150</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F4" s="12">
-        <f>B4*D4</f>
+      <c r="B4" s="11">
+        <f>IF($A4="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A4))</f>
+        <v/>
+      </c>
+      <c r="C4" s="11">
+        <f>IF($A4="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A4),0))</f>
+        <v/>
+      </c>
+      <c r="D4" s="19">
+        <f>IF($A4="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A4,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E4" s="19">
+        <f>IF($A4="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A4),0))</f>
+        <v/>
+      </c>
+      <c r="F4" s="19">
+        <f>IF($A4="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A4,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
         <v/>
       </c>
       <c r="G4" s="12">
         <f>F4*12</f>
         <v/>
       </c>
-      <c r="H4" s="12">
-        <f>B4*E4</f>
+      <c r="H4" s="19">
+        <f>IF($A4="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A4))</f>
         <v/>
       </c>
       <c r="I4" s="12">
@@ -2960,33 +7159,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>2 BD / 1 BA</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="C5" s="18" t="n">
-        <v>950</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>1400</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>1575</v>
-      </c>
-      <c r="F5" s="12">
-        <f>B5*D5</f>
+      <c r="B5" s="11">
+        <f>IF($A5="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A5))</f>
+        <v/>
+      </c>
+      <c r="C5" s="11">
+        <f>IF($A5="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A5),0))</f>
+        <v/>
+      </c>
+      <c r="D5" s="19">
+        <f>IF($A5="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A5,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E5" s="19">
+        <f>IF($A5="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A5),0))</f>
+        <v/>
+      </c>
+      <c r="F5" s="19">
+        <f>IF($A5="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A5,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
         <v/>
       </c>
       <c r="G5" s="12">
         <f>F5*12</f>
         <v/>
       </c>
-      <c r="H5" s="12">
-        <f>B5*E5</f>
+      <c r="H5" s="19">
+        <f>IF($A5="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A5))</f>
         <v/>
       </c>
       <c r="I5" s="12">
@@ -2995,33 +7198,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>2 BD / 2 BA</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1550</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>1725</v>
-      </c>
-      <c r="F6" s="12">
-        <f>B6*D6</f>
+      <c r="B6" s="11">
+        <f>IF($A6="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A6))</f>
+        <v/>
+      </c>
+      <c r="C6" s="11">
+        <f>IF($A6="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A6),0))</f>
+        <v/>
+      </c>
+      <c r="D6" s="19">
+        <f>IF($A6="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A6,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E6" s="19">
+        <f>IF($A6="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A6),0))</f>
+        <v/>
+      </c>
+      <c r="F6" s="19">
+        <f>IF($A6="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A6,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
         <v/>
       </c>
       <c r="G6" s="12">
         <f>F6*12</f>
         <v/>
       </c>
-      <c r="H6" s="12">
-        <f>B6*E6</f>
+      <c r="H6" s="19">
+        <f>IF($A6="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A6))</f>
         <v/>
       </c>
       <c r="I6" s="12">
@@ -3030,33 +7237,37 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>3 BD / 2 BA</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>1250</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>1850</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>2050</v>
-      </c>
-      <c r="F7" s="12">
-        <f>B7*D7</f>
+      <c r="B7" s="11">
+        <f>IF($A7="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A7))</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>IF($A7="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A7),0))</f>
+        <v/>
+      </c>
+      <c r="D7" s="19">
+        <f>IF($A7="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A7,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E7" s="19">
+        <f>IF($A7="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A7),0))</f>
+        <v/>
+      </c>
+      <c r="F7" s="19">
+        <f>IF($A7="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A7,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
         <v/>
       </c>
       <c r="G7" s="12">
         <f>F7*12</f>
         <v/>
       </c>
-      <c r="H7" s="12">
-        <f>B7*E7</f>
+      <c r="H7" s="19">
+        <f>IF($A7="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A7))</f>
         <v/>
       </c>
       <c r="I7" s="12">
@@ -3065,64 +7276,367 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="11">
+        <f>IF($A8="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A8))</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>IF($A8="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A8),0))</f>
+        <v/>
+      </c>
+      <c r="D8" s="19">
+        <f>IF($A8="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A8,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E8" s="19">
+        <f>IF($A8="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A8),0))</f>
+        <v/>
+      </c>
+      <c r="F8" s="19">
+        <f>IF($A8="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A8,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>F8*12</f>
+        <v/>
+      </c>
+      <c r="H8" s="19">
+        <f>IF($A8="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A8))</f>
+        <v/>
+      </c>
+      <c r="I8" s="12">
+        <f>H8*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n"/>
+      <c r="B9" s="11">
+        <f>IF($A9="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A9))</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>IF($A9="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A9),0))</f>
+        <v/>
+      </c>
+      <c r="D9" s="19">
+        <f>IF($A9="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A9,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E9" s="19">
+        <f>IF($A9="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A9),0))</f>
+        <v/>
+      </c>
+      <c r="F9" s="19">
+        <f>IF($A9="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A9,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>F9*12</f>
+        <v/>
+      </c>
+      <c r="H9" s="19">
+        <f>IF($A9="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A9))</f>
+        <v/>
+      </c>
+      <c r="I9" s="12">
+        <f>H9*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="11">
+        <f>IF($A10="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A10))</f>
+        <v/>
+      </c>
+      <c r="C10" s="11">
+        <f>IF($A10="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A10),0))</f>
+        <v/>
+      </c>
+      <c r="D10" s="19">
+        <f>IF($A10="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A10,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>IF($A10="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A10),0))</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>IF($A10="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A10,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="12">
+        <f>F10*12</f>
+        <v/>
+      </c>
+      <c r="H10" s="19">
+        <f>IF($A10="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A10))</f>
+        <v/>
+      </c>
+      <c r="I10" s="12">
+        <f>H10*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n"/>
+      <c r="B11" s="11">
+        <f>IF($A11="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A11))</f>
+        <v/>
+      </c>
+      <c r="C11" s="11">
+        <f>IF($A11="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A11),0))</f>
+        <v/>
+      </c>
+      <c r="D11" s="19">
+        <f>IF($A11="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A11,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f>IF($A11="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A11),0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="19">
+        <f>IF($A11="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A11,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
+        <v/>
+      </c>
+      <c r="G11" s="12">
+        <f>F11*12</f>
+        <v/>
+      </c>
+      <c r="H11" s="19">
+        <f>IF($A11="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="12">
+        <f>H11*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="11">
+        <f>IF($A12="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A12))</f>
+        <v/>
+      </c>
+      <c r="C12" s="11">
+        <f>IF($A12="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A12),0))</f>
+        <v/>
+      </c>
+      <c r="D12" s="19">
+        <f>IF($A12="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A12,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E12" s="19">
+        <f>IF($A12="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A12),0))</f>
+        <v/>
+      </c>
+      <c r="F12" s="19">
+        <f>IF($A12="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A12,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>F12*12</f>
+        <v/>
+      </c>
+      <c r="H12" s="19">
+        <f>IF($A12="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="12">
+        <f>H12*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n"/>
+      <c r="B13" s="11">
+        <f>IF($A13="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A13))</f>
+        <v/>
+      </c>
+      <c r="C13" s="11">
+        <f>IF($A13="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A13),0))</f>
+        <v/>
+      </c>
+      <c r="D13" s="19">
+        <f>IF($A13="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A13,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E13" s="19">
+        <f>IF($A13="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A13),0))</f>
+        <v/>
+      </c>
+      <c r="F13" s="19">
+        <f>IF($A13="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A13,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>F13*12</f>
+        <v/>
+      </c>
+      <c r="H13" s="19">
+        <f>IF($A13="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A13))</f>
+        <v/>
+      </c>
+      <c r="I13" s="12">
+        <f>H13*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n"/>
+      <c r="B14" s="11">
+        <f>IF($A14="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A14))</f>
+        <v/>
+      </c>
+      <c r="C14" s="11">
+        <f>IF($A14="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A14),0))</f>
+        <v/>
+      </c>
+      <c r="D14" s="19">
+        <f>IF($A14="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A14,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E14" s="19">
+        <f>IF($A14="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A14),0))</f>
+        <v/>
+      </c>
+      <c r="F14" s="19">
+        <f>IF($A14="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A14,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>F14*12</f>
+        <v/>
+      </c>
+      <c r="H14" s="19">
+        <f>IF($A14="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A14))</f>
+        <v/>
+      </c>
+      <c r="I14" s="12">
+        <f>H14*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="11">
+        <f>IF($A15="",0,COUNTIF('Rent Roll (Input)'!$B$5:$B$504,$A15))</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>IF($A15="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$E$5:$E$504,'Rent Roll (Input)'!$B$5:$B$504,$A15),0))</f>
+        <v/>
+      </c>
+      <c r="D15" s="19">
+        <f>IF($A15="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A15,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"),0))</f>
+        <v/>
+      </c>
+      <c r="E15" s="19">
+        <f>IF($A15="",0,IFERROR(AVERAGEIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A15),0))</f>
+        <v/>
+      </c>
+      <c r="F15" s="19">
+        <f>IF($A15="",0,SUMIFS('Rent Roll (Input)'!$G$5:$G$504,'Rent Roll (Input)'!$B$5:$B$504,$A15,'Rent Roll (Input)'!$F$5:$F$504,"Occupied"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="12">
+        <f>F15*12</f>
+        <v/>
+      </c>
+      <c r="H15" s="19">
+        <f>IF($A15="",0,SUMIFS('Rent Roll (Input)'!$H$5:$H$504,'Rent Roll (Input)'!$B$5:$B$504,$A15))</f>
+        <v/>
+      </c>
+      <c r="I15" s="12">
+        <f>H15*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Total / Weighted</t>
         </is>
       </c>
-      <c r="B8" s="22">
-        <f>SUM(B4:B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="22">
-        <f>SUMPRODUCT(B4:B7,C4:C7)/B8</f>
-        <v/>
-      </c>
-      <c r="D8" s="23">
-        <f>F8/B8</f>
-        <v/>
-      </c>
-      <c r="E8" s="23">
-        <f>H8/B8</f>
-        <v/>
-      </c>
-      <c r="F8" s="24">
-        <f>SUM(F4:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="24">
-        <f>SUM(G4:G7)</f>
-        <v/>
-      </c>
-      <c r="H8" s="24">
-        <f>SUM(H4:H7)</f>
-        <v/>
-      </c>
-      <c r="I8" s="24">
-        <f>SUM(I4:I7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="B16" s="24">
+        <f>SUM(B4:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="24">
+        <f>IFERROR(SUMPRODUCT(B4:B15,C4:C15)/B16,0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="26">
+        <f>IFERROR(F16/B16,0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="26">
+        <f>IFERROR(H16/B16,0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="28">
+        <f>SUM(F4:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="28">
+        <f>SUM(G4:G15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="28">
+        <f>SUM(H4:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="28">
+        <f>SUM(I4:I15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>Loss-to-Lease (Market - In-Place, annual)</t>
         </is>
       </c>
-      <c r="I10" s="26">
-        <f>I8-G8</f>
+      <c r="I18" s="30">
+        <f>I16-G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Units in Rent Roll (all rows)</t>
+        </is>
+      </c>
+      <c r="B20" s="11">
+        <f>'Rent Roll (Input)'!$N$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Check: mapped = rent roll?</t>
+        </is>
+      </c>
+      <c r="B21" s="27">
+        <f>IF(B16='Rent Roll (Input)'!$N$7,"OK — all units mapped","ADD missing floor plan(s) to col A")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3159,32 +7673,32 @@
       <c r="F3" s="7" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Unit Type</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t># Units to Reno</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>Reno Cost/Unit</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>Rent Premium ($/mo)</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>Reno Budget</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>Annual Premium (gross)</t>
         </is>
@@ -3287,26 +7801,26 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="28">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="28">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Blended cost / renovated unit</t>
         </is>
@@ -3334,39 +7848,39 @@
       <c r="K12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="28" t="n">
+      <c r="B13" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="I13" s="28" t="n">
+      <c r="I13" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="28" t="n">
+      <c r="J13" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="K13" s="28" t="n">
+      <c r="K13" s="32" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3413,43 +7927,43 @@
           <t>Cumulative Units Renovated</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="33">
         <f>$B$9*B14</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="33">
         <f>$B$9*C14</f>
         <v/>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="33">
         <f>$B$9*D14</f>
         <v/>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="33">
         <f>$B$9*E14</f>
         <v/>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="33">
         <f>$B$9*F14</f>
         <v/>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="33">
         <f>$B$9*G14</f>
         <v/>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="33">
         <f>$B$9*H14</f>
         <v/>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="33">
         <f>$B$9*I14</f>
         <v/>
       </c>
-      <c r="J15" s="29">
+      <c r="J15" s="33">
         <f>$B$9*J14</f>
         <v/>
       </c>
-      <c r="K15" s="29">
+      <c r="K15" s="33">
         <f>$B$9*K14</f>
         <v/>
       </c>
@@ -3549,7 +8063,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Net Premium to EGI</t>
         </is>
@@ -3603,7 +8117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3627,27 +8141,27 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>In-Place (T-12)</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>Year-1 Underwritten</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Per Unit (UW)</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3672,19 +8186,19 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>'RR'!$G$8</t>
+          <t>'RR'!$G$16</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>'RR'!$I$8</t>
+          <t>'RR'!$I$16</t>
         </is>
       </c>
       <c r="D5" s="12">
-        <f>C5/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E5" s="30" t="inlineStr">
+        <f>C5/'RR'!$B$16</f>
+        <v/>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>In-place=RR in-place annual; UW=RR as-is market annual.</t>
         </is>
@@ -3705,10 +8219,10 @@
         <v/>
       </c>
       <c r="D6" s="12">
-        <f>C6/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E6" s="30" t="inlineStr">
+        <f>C6/'RR'!$B$16</f>
+        <v/>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Economic vacancy.</t>
         </is>
@@ -3729,26 +8243,26 @@
         <v/>
       </c>
       <c r="D7" s="12">
-        <f>C7/'RR'!$B$8</f>
+        <f>C7/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Net Rental Income</t>
         </is>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="26">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="26">
         <f>SUM(C5:C7)</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>C8/'RR'!$B$8</f>
+        <f>C8/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3766,31 +8280,31 @@
         <v/>
       </c>
       <c r="D9" s="12">
-        <f>C9/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
+        <f>C9/'RR'!$B$16</f>
+        <v/>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>Type T-12 actual; UW grows it one year.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Effective Gross Income (EGI)</t>
         </is>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="26">
         <f>B8+B9</f>
         <v/>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="26">
         <f>C8+C9</f>
         <v/>
       </c>
       <c r="D10" s="12">
-        <f>C10/'RR'!$B$8</f>
+        <f>C10/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3819,7 +8333,7 @@
         <v/>
       </c>
       <c r="D13" s="12">
-        <f>C13/'RR'!$B$8</f>
+        <f>C13/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3837,7 +8351,7 @@
         <v/>
       </c>
       <c r="D14" s="12">
-        <f>C14/'RR'!$B$8</f>
+        <f>C14/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3855,7 +8369,7 @@
         <v/>
       </c>
       <c r="D15" s="12">
-        <f>C15/'RR'!$B$8</f>
+        <f>C15/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3873,7 +8387,7 @@
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>C16/'RR'!$B$8</f>
+        <f>C16/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3891,7 +8405,7 @@
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>C17/'RR'!$B$8</f>
+        <f>C17/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3909,7 +8423,7 @@
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>C18/'RR'!$B$8</f>
+        <f>C18/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3927,7 +8441,7 @@
         <v/>
       </c>
       <c r="D19" s="12">
-        <f>C19/'RR'!$B$8</f>
+        <f>C19/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3945,7 +8459,7 @@
         <v/>
       </c>
       <c r="D20" s="12">
-        <f>C20/'RR'!$B$8</f>
+        <f>C20/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -3964,10 +8478,10 @@
         <v/>
       </c>
       <c r="D21" s="12">
-        <f>C21/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E21" s="30" t="inlineStr">
+        <f>C21/'RR'!$B$16</f>
+        <v/>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>Computed as % of EGI.</t>
         </is>
@@ -3980,58 +8494,58 @@
         </is>
       </c>
       <c r="B22" s="19">
-        <f>'RR'!$B$8*'Assumptions'!$B$19</f>
+        <f>'RR'!$B$16*'Assumptions'!$B$19</f>
         <v/>
       </c>
       <c r="C22" s="19">
-        <f>'RR'!$B$8*'Assumptions'!$B$19</f>
+        <f>'RR'!$B$16*'Assumptions'!$B$19</f>
         <v/>
       </c>
       <c r="D22" s="12">
-        <f>C22/'RR'!$B$8</f>
-        <v/>
-      </c>
-      <c r="E22" s="30" t="inlineStr">
+        <f>C22/'RR'!$B$16</f>
+        <v/>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>Units x reserves/unit.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="28">
         <f>SUM(B13:B22)</f>
         <v/>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="28">
         <f>SUM(C13:C22)</f>
         <v/>
       </c>
       <c r="D23" s="12">
-        <f>C23/'RR'!$B$8</f>
+        <f>C23/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>NET OPERATING INCOME (NOI)</t>
         </is>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="34">
         <f>B10-B23</f>
         <v/>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="34">
         <f>C10-C23</f>
         <v/>
       </c>
       <c r="D24" s="12">
-        <f>C24/'RR'!$B$8</f>
+        <f>C24/'RR'!$B$16</f>
         <v/>
       </c>
     </row>
@@ -4041,11 +8555,11 @@
           <t>Operating Expense Ratio</t>
         </is>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="35">
         <f>B23/B10</f>
         <v/>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="35">
         <f>C23/C10</f>
         <v/>
       </c>
@@ -4058,7 +8572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4088,57 +8602,57 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t>Year 6</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
-      <c r="I3" s="20" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t>Year 8</t>
         </is>
       </c>
-      <c r="J3" s="20" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t>Year 9</t>
         </is>
       </c>
-      <c r="K3" s="20" t="inlineStr">
+      <c r="K3" s="21" t="inlineStr">
         <is>
           <t>Year 10</t>
         </is>
@@ -4239,48 +8753,48 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Effective Gross Income</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="26">
         <f>B4+B5</f>
         <v/>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="26">
         <f>C4+C5</f>
         <v/>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="26">
         <f>D4+D5</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="26">
         <f>E4+E5</f>
         <v/>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="26">
         <f>F4+F5</f>
         <v/>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="26">
         <f>G4+G5</f>
         <v/>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="26">
         <f>H4+H5</f>
         <v/>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="26">
         <f>I4+I5</f>
         <v/>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="26">
         <f>J4+J5</f>
         <v/>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="26">
         <f>K4+K5</f>
         <v/>
       </c>
@@ -4333,102 +8847,102 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="28">
         <f>B6-B7</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="28">
         <f>C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="28">
         <f>D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="28">
         <f>E6-E7</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="28">
         <f>F6-F7</f>
         <v/>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="28">
         <f>G6-G7</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="28">
         <f>H6-H7</f>
         <v/>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="28">
         <f>I6-I7</f>
         <v/>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="28">
         <f>J6-J7</f>
         <v/>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="28">
         <f>K6-K7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>NOI Growth %</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="35">
         <f>C8/B8-1</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="35">
         <f>D8/C8-1</f>
         <v/>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="35">
         <f>E8/D8-1</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="35">
         <f>F8/E8-1</f>
         <v/>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="35">
         <f>G8/F8-1</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="35">
         <f>H8/G8-1</f>
         <v/>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="35">
         <f>I8/H8-1</f>
         <v/>
       </c>
-      <c r="J9" s="32">
+      <c r="J9" s="35">
         <f>J8/I8-1</f>
         <v/>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="35">
         <f>K8/J8-1</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>(memo) Reno Capex Draw</t>
         </is>
@@ -4482,7 +8996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4546,12 +9060,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Total Uses</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="28">
         <f>SUM(B4:B6)</f>
         <v/>
       </c>
@@ -4574,7 +9088,7 @@
         <f>'Assumptions'!$B$4*'Assumptions'!$B$22</f>
         <v/>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="35">
         <f>B10/B7</f>
         <v/>
       </c>
@@ -4593,7 +9107,7 @@
         <f>B7-B10</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="35">
         <f>B11/B7</f>
         <v/>
       </c>
@@ -4603,18 +9117,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Total Sources</t>
         </is>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="28">
         <f>SUM(B10:B11)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Check (Sources - Uses)</t>
         </is>
@@ -4632,7 +9146,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4675,7 +9189,7 @@
           <t>Interest Rate</t>
         </is>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="37">
         <f>'Assumptions'!$B$23</f>
         <v/>
       </c>
@@ -4724,7 +9238,7 @@
           <t>Monthly Amortizing Payment</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="38">
         <f>PMT(B5/12,B6*12,-B4)</f>
         <v/>
       </c>
@@ -4751,12 +9265,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Annual Debt Service — Amortizing</t>
         </is>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="39">
         <f>B9*12</f>
         <v/>
       </c>
@@ -4772,7 +9286,7 @@
           <t>DSCR — Year 1 (actual)</t>
         </is>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="40">
         <f>'Pro Forma'!$B$8/IF(1&lt;=B7,B10,B11)</f>
         <v/>
       </c>
@@ -4788,7 +9302,7 @@
           <t>DSCR — Amortizing (stress)</t>
         </is>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="40">
         <f>'Pro Forma'!$B$8/B11</f>
         <v/>
       </c>
@@ -4804,7 +9318,7 @@
           <t>Debt Yield (Year-1 NOI)</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="35">
         <f>'Pro Forma'!$B$8/B4</f>
         <v/>
       </c>
@@ -4836,696 +9350,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Returns  —  levered &amp; unlevered (exits in the hold year)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>Line Item</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>Year 0</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>Year 6</t>
-        </is>
-      </c>
-      <c r="I3" s="20" t="inlineStr">
-        <is>
-          <t>Year 7</t>
-        </is>
-      </c>
-      <c r="J3" s="20" t="inlineStr">
-        <is>
-          <t>Year 8</t>
-        </is>
-      </c>
-      <c r="K3" s="20" t="inlineStr">
-        <is>
-          <t>Year 9</t>
-        </is>
-      </c>
-      <c r="L3" s="20" t="inlineStr">
-        <is>
-          <t>Year 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>Year #</t>
-        </is>
-      </c>
-      <c r="B4" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="38" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="J4" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" s="38" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>NOI (from Pro Forma)</t>
-        </is>
-      </c>
-      <c r="C5" s="12">
-        <f>IF(AND(C$4&gt;=1,C$4&lt;='Assumptions'!$B$8),'Pro Forma'!B8,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="12">
-        <f>IF(AND(D$4&gt;=1,D$4&lt;='Assumptions'!$B$8),'Pro Forma'!C8,0)</f>
-        <v/>
-      </c>
-      <c r="E5" s="12">
-        <f>IF(AND(E$4&gt;=1,E$4&lt;='Assumptions'!$B$8),'Pro Forma'!D8,0)</f>
-        <v/>
-      </c>
-      <c r="F5" s="12">
-        <f>IF(AND(F$4&gt;=1,F$4&lt;='Assumptions'!$B$8),'Pro Forma'!E8,0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="12">
-        <f>IF(AND(G$4&gt;=1,G$4&lt;='Assumptions'!$B$8),'Pro Forma'!F8,0)</f>
-        <v/>
-      </c>
-      <c r="H5" s="12">
-        <f>IF(AND(H$4&gt;=1,H$4&lt;='Assumptions'!$B$8),'Pro Forma'!G8,0)</f>
-        <v/>
-      </c>
-      <c r="I5" s="12">
-        <f>IF(AND(I$4&gt;=1,I$4&lt;='Assumptions'!$B$8),'Pro Forma'!H8,0)</f>
-        <v/>
-      </c>
-      <c r="J5" s="12">
-        <f>IF(AND(J$4&gt;=1,J$4&lt;='Assumptions'!$B$8),'Pro Forma'!I8,0)</f>
-        <v/>
-      </c>
-      <c r="K5" s="12">
-        <f>IF(AND(K$4&gt;=1,K$4&lt;='Assumptions'!$B$8),'Pro Forma'!J8,0)</f>
-        <v/>
-      </c>
-      <c r="L5" s="12">
-        <f>IF(AND(L$4&gt;=1,L$4&lt;='Assumptions'!$B$8),'Pro Forma'!K8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Debt Service</t>
-        </is>
-      </c>
-      <c r="C6" s="12">
-        <f>IF(AND(C$4&gt;=1,C$4&lt;='Assumptions'!$B$8),-IF(C$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="12">
-        <f>IF(AND(D$4&gt;=1,D$4&lt;='Assumptions'!$B$8),-IF(D$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="12">
-        <f>IF(AND(E$4&gt;=1,E$4&lt;='Assumptions'!$B$8),-IF(E$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
-        <f>IF(AND(F$4&gt;=1,F$4&lt;='Assumptions'!$B$8),-IF(F$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="12">
-        <f>IF(AND(G$4&gt;=1,G$4&lt;='Assumptions'!$B$8),-IF(G$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-      <c r="H6" s="12">
-        <f>IF(AND(H$4&gt;=1,H$4&lt;='Assumptions'!$B$8),-IF(H$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="12">
-        <f>IF(AND(I$4&gt;=1,I$4&lt;='Assumptions'!$B$8),-IF(I$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-      <c r="J6" s="12">
-        <f>IF(AND(J$4&gt;=1,J$4&lt;='Assumptions'!$B$8),-IF(J$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-      <c r="K6" s="12">
-        <f>IF(AND(K$4&gt;=1,K$4&lt;='Assumptions'!$B$8),-IF(K$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-      <c r="L6" s="12">
-        <f>IF(AND(L$4&gt;=1,L$4&lt;='Assumptions'!$B$8),-IF(L$4&lt;='Assumptions'!$B$25,'Debt'!$B$10,'Debt'!$B$11),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Operating CF (levered)</t>
-        </is>
-      </c>
-      <c r="C7" s="12">
-        <f>C5+C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="12">
-        <f>D5+D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="12">
-        <f>E5+E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
-        <f>F5+F6</f>
-        <v/>
-      </c>
-      <c r="G7" s="12">
-        <f>G5+G6</f>
-        <v/>
-      </c>
-      <c r="H7" s="12">
-        <f>H5+H6</f>
-        <v/>
-      </c>
-      <c r="I7" s="12">
-        <f>I5+I6</f>
-        <v/>
-      </c>
-      <c r="J7" s="12">
-        <f>J5+J6</f>
-        <v/>
-      </c>
-      <c r="K7" s="12">
-        <f>K5+K6</f>
-        <v/>
-      </c>
-      <c r="L7" s="12">
-        <f>L5+L6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Gross Sale Price (exit)</t>
-        </is>
-      </c>
-      <c r="C8" s="12">
-        <f>IF(C$4='Assumptions'!$B$8,C5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="12">
-        <f>IF(D$4='Assumptions'!$B$8,D5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="12">
-        <f>IF(E$4='Assumptions'!$B$8,E5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
-        <f>IF(F$4='Assumptions'!$B$8,F5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="12">
-        <f>IF(G$4='Assumptions'!$B$8,G5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="H8" s="12">
-        <f>IF(H$4='Assumptions'!$B$8,H5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="12">
-        <f>IF(I$4='Assumptions'!$B$8,I5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="12">
-        <f>IF(J$4='Assumptions'!$B$8,J5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="12">
-        <f>IF(K$4='Assumptions'!$B$8,K5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="L8" s="12">
-        <f>IF(L$4='Assumptions'!$B$8,L5/'Assumptions'!$B$9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Less: Selling Costs</t>
-        </is>
-      </c>
-      <c r="C9" s="12">
-        <f>-C8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-      <c r="D9" s="12">
-        <f>-D8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-      <c r="E9" s="12">
-        <f>-E8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
-        <f>-F8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-      <c r="G9" s="12">
-        <f>-G8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-      <c r="H9" s="12">
-        <f>-H8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-      <c r="I9" s="12">
-        <f>-I8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-      <c r="J9" s="12">
-        <f>-J8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-      <c r="K9" s="12">
-        <f>-K8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-      <c r="L9" s="12">
-        <f>-L8*'Assumptions'!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Less: Loan Payoff</t>
-        </is>
-      </c>
-      <c r="C10" s="12">
-        <f>IF(C$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="12">
-        <f>IF(D$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="E10" s="12">
-        <f>IF(E$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
-        <f>IF(F$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="12">
-        <f>IF(G$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="H10" s="12">
-        <f>IF(H$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="I10" s="12">
-        <f>IF(I$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="12">
-        <f>IF(J$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="K10" s="12">
-        <f>IF(K$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="L10" s="12">
-        <f>IF(L$4='Assumptions'!$B$8,-'Debt'!$B$15,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Net Sale Proceeds</t>
-        </is>
-      </c>
-      <c r="C11" s="12">
-        <f>C8+C9+C10</f>
-        <v/>
-      </c>
-      <c r="D11" s="12">
-        <f>D8+D9+D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="12">
-        <f>E8+E9+E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="12">
-        <f>F8+F9+F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="12">
-        <f>G8+G9+G10</f>
-        <v/>
-      </c>
-      <c r="H11" s="12">
-        <f>H8+H9+H10</f>
-        <v/>
-      </c>
-      <c r="I11" s="12">
-        <f>I8+I9+I10</f>
-        <v/>
-      </c>
-      <c r="J11" s="12">
-        <f>J8+J9+J10</f>
-        <v/>
-      </c>
-      <c r="K11" s="12">
-        <f>K8+K9+K10</f>
-        <v/>
-      </c>
-      <c r="L11" s="12">
-        <f>L8+L9+L10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Net Levered Cash Flow</t>
-        </is>
-      </c>
-      <c r="B12" s="39">
-        <f>-'Sources &amp; Uses'!$B$11</f>
-        <v/>
-      </c>
-      <c r="C12" s="24">
-        <f>C7+C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>D7+D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>E7+E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="24">
-        <f>F7+F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="24">
-        <f>G7+G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="24">
-        <f>H7+H11</f>
-        <v/>
-      </c>
-      <c r="I12" s="24">
-        <f>I7+I11</f>
-        <v/>
-      </c>
-      <c r="J12" s="24">
-        <f>J7+J11</f>
-        <v/>
-      </c>
-      <c r="K12" s="24">
-        <f>K7+K11</f>
-        <v/>
-      </c>
-      <c r="L12" s="24">
-        <f>L7+L11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Net Unlevered Cash Flow</t>
-        </is>
-      </c>
-      <c r="B13" s="39">
-        <f>-'Sources &amp; Uses'!$B$7</f>
-        <v/>
-      </c>
-      <c r="C13" s="24">
-        <f>C5+C8+C9</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>D5+D8+D9</f>
-        <v/>
-      </c>
-      <c r="E13" s="24">
-        <f>E5+E8+E9</f>
-        <v/>
-      </c>
-      <c r="F13" s="24">
-        <f>F5+F8+F9</f>
-        <v/>
-      </c>
-      <c r="G13" s="24">
-        <f>G5+G8+G9</f>
-        <v/>
-      </c>
-      <c r="H13" s="24">
-        <f>H5+H8+H9</f>
-        <v/>
-      </c>
-      <c r="I13" s="24">
-        <f>I5+I8+I9</f>
-        <v/>
-      </c>
-      <c r="J13" s="24">
-        <f>J5+J8+J9</f>
-        <v/>
-      </c>
-      <c r="K13" s="24">
-        <f>K5+K8+K9</f>
-        <v/>
-      </c>
-      <c r="L13" s="24">
-        <f>L5+L8+L9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>RETURN METRICS</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B16" s="40">
-        <f>IRR(B12:L12)</f>
-        <v/>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Annualized return to equity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Levered Equity Multiple</t>
-        </is>
-      </c>
-      <c r="B17" s="41">
-        <f>SUM(C12:L12)/'Sources &amp; Uses'!$B$11</f>
-        <v/>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Total cash returned / equity in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Avg Cash-on-Cash (levered)</t>
-        </is>
-      </c>
-      <c r="B18" s="40">
-        <f>SUM(C7:L7)/'Assumptions'!$B$8/'Sources &amp; Uses'!$B$11</f>
-        <v/>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Avg annual operating CF / equity over the hold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="40">
-        <f>IRR(B13:L13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Unlevered Equity Multiple</t>
-        </is>
-      </c>
-      <c r="B20" s="41">
-        <f>SUM(C13:L13)/'Sources &amp; Uses'!$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Going-in Cap (as-is)</t>
-        </is>
-      </c>
-      <c r="B21" s="42">
-        <f>'Assumptions'!$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Exit Cap</t>
-        </is>
-      </c>
-      <c r="B22" s="42">
-        <f>'Assumptions'!$B$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Hold Period (yrs)</t>
-        </is>
-      </c>
-      <c r="B23" s="22">
-        <f>'Assumptions'!$B$8</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/templates/UW_Model_Template.xlsx
+++ b/templates/UW_Model_Template.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="167" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00404040"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -183,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -225,23 +231,25 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -262,7 +270,7 @@
     <xf numFmtId="165" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -698,7 +706,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="37.5" customHeight="1">
+    <row r="9" ht="62.5" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Rent Roll (Input)</t>
@@ -706,7 +714,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Paste ANY property's rent roll here — one row per unit (unit #, floor plan, SF, status, in-place rent, market rent, lease dates). Nothing to calculate; it is the raw data source. The Floor-Plan text is the key the RR tab groups on.</t>
+          <t>Paste ANY property's rent roll here — one row per unit (unit #, floor plan, SF, status, in-place rent, market rent, lease dates). The Floor-Plan text is the key the RR tab groups on. Side sections (cols M-O) hold Other Income, Concessions, and Employee/Model Discounts — enter any monthly charges there; their totals flow to the P&amp;L (other income, and the in-place concessions line).</t>
         </is>
       </c>
     </row>
@@ -951,42 +959,42 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Year #</t>
         </is>
       </c>
-      <c r="B4" s="41" t="n">
+      <c r="B4" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="41" t="n">
+      <c r="C4" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="41" t="n">
+      <c r="E4" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="41" t="n">
+      <c r="F4" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="41" t="n">
+      <c r="G4" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="41" t="n">
+      <c r="H4" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="I4" s="41" t="n">
+      <c r="I4" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="J4" s="41" t="n">
+      <c r="J4" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="41" t="n">
+      <c r="K4" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="L4" s="41" t="n">
+      <c r="L4" s="43" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1320,103 +1328,103 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Net Levered Cash Flow</t>
         </is>
       </c>
-      <c r="B12" s="42">
+      <c r="B12" s="44">
         <f>-'Sources &amp; Uses'!$B$11</f>
         <v/>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="30">
         <f>C7+C11</f>
         <v/>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="30">
         <f>D7+D11</f>
         <v/>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="30">
         <f>E7+E11</f>
         <v/>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="30">
         <f>F7+F11</f>
         <v/>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="30">
         <f>G7+G11</f>
         <v/>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="30">
         <f>H7+H11</f>
         <v/>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="30">
         <f>I7+I11</f>
         <v/>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="30">
         <f>J7+J11</f>
         <v/>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="30">
         <f>K7+K11</f>
         <v/>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="30">
         <f>L7+L11</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Net Unlevered Cash Flow</t>
         </is>
       </c>
-      <c r="B13" s="42">
+      <c r="B13" s="44">
         <f>-'Sources &amp; Uses'!$B$7</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="30">
         <f>C5+C8+C9</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="30">
         <f>D5+D8+D9</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="30">
         <f>E5+E8+E9</f>
         <v/>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="30">
         <f>F5+F8+F9</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="30">
         <f>G5+G8+G9</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="30">
         <f>H5+H8+H9</f>
         <v/>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="30">
         <f>I5+I8+I9</f>
         <v/>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="30">
         <f>J5+J8+J9</f>
         <v/>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="30">
         <f>K5+K8+K9</f>
         <v/>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="30">
         <f>L5+L8+L9</f>
         <v/>
       </c>
@@ -1461,7 +1469,7 @@
           <t>Levered Equity Multiple</t>
         </is>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="45">
         <f>SUM(C12:L12)/'Sources &amp; Uses'!$B$11</f>
         <v/>
       </c>
@@ -1504,7 +1512,7 @@
           <t>Unlevered Equity Multiple</t>
         </is>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="45">
         <f>SUM(C13:L13)/'Sources &amp; Uses'!$B$7</f>
         <v/>
       </c>
@@ -1515,7 +1523,7 @@
           <t>Going-in Cap (as-is)</t>
         </is>
       </c>
-      <c r="B21" s="44">
+      <c r="B21" s="46">
         <f>'Assumptions'!$B$7</f>
         <v/>
       </c>
@@ -1526,7 +1534,7 @@
           <t>Exit Cap</t>
         </is>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="46">
         <f>'Assumptions'!$B$9</f>
         <v/>
       </c>
@@ -1576,148 +1584,148 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>Growth \ Exit Cap</t>
         </is>
       </c>
-      <c r="C5" s="46" t="n">
+      <c r="C5" s="48" t="n">
         <v>0.05</v>
       </c>
-      <c r="D5" s="46" t="n">
+      <c r="D5" s="48" t="n">
         <v>0.055</v>
       </c>
-      <c r="E5" s="46" t="n">
+      <c r="E5" s="48" t="n">
         <v>0.06</v>
       </c>
-      <c r="F5" s="46" t="n">
+      <c r="F5" s="48" t="n">
         <v>0.065</v>
       </c>
-      <c r="G5" s="46" t="n">
+      <c r="G5" s="48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="49" t="n">
         <v>0.01</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="50">
         <f>B$33</f>
         <v/>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="50">
         <f>C$33</f>
         <v/>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="50">
         <f>D$33</f>
         <v/>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="50">
         <f>E$33</f>
         <v/>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="50">
         <f>F$33</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="49" t="n">
         <v>0.02</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="50">
         <f>G$33</f>
         <v/>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="50">
         <f>H$33</f>
         <v/>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="50">
         <f>I$33</f>
         <v/>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="50">
         <f>J$33</f>
         <v/>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="50">
         <f>K$33</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="49" t="n">
         <v>0.03</v>
       </c>
-      <c r="C8" s="48">
+      <c r="C8" s="50">
         <f>L$33</f>
         <v/>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="50">
         <f>M$33</f>
         <v/>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="51">
         <f>N$33</f>
         <v/>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="50">
         <f>O$33</f>
         <v/>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="50">
         <f>P$33</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="49" t="n">
         <v>0.04</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="50">
         <f>Q$33</f>
         <v/>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="50">
         <f>R$33</f>
         <v/>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="50">
         <f>S$33</f>
         <v/>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="50">
         <f>T$33</f>
         <v/>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="50">
         <f>U$33</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="49" t="n">
         <v>0.05</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="50">
         <f>V$33</f>
         <v/>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="50">
         <f>W$33</f>
         <v/>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="50">
         <f>X$33</f>
         <v/>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="50">
         <f>Y$33</f>
         <v/>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="50">
         <f>Z$33</f>
         <v/>
       </c>
@@ -1762,7 +1770,7 @@
       <c r="Z19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Rent Growth (g)</t>
         </is>
@@ -1869,7 +1877,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Exit Cap (X)</t>
         </is>
@@ -1976,7 +1984,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>CF Year 0</t>
         </is>
@@ -2083,7 +2091,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>CF Year 1</t>
         </is>
@@ -2190,7 +2198,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>CF Year 2</t>
         </is>
@@ -2297,7 +2305,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>CF Year 3</t>
         </is>
@@ -2404,7 +2412,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>CF Year 4</t>
         </is>
@@ -2511,7 +2519,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>CF Year 5</t>
         </is>
@@ -2618,7 +2626,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>CF Year 6</t>
         </is>
@@ -2725,7 +2733,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>CF Year 7</t>
         </is>
@@ -2832,7 +2840,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>CF Year 8</t>
         </is>
@@ -2939,7 +2947,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>CF Year 9</t>
         </is>
@@ -3046,7 +3054,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>CF Year 10</t>
         </is>
@@ -3153,108 +3161,108 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="inlineStr">
+      <c r="A33" s="52" t="inlineStr">
         <is>
           <t>Levered IRR</t>
         </is>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="37">
         <f>IRR(B22:B32)</f>
         <v/>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="37">
         <f>IRR(C22:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="37">
         <f>IRR(D22:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="37">
         <f>IRR(E22:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="37">
         <f>IRR(F22:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="37">
         <f>IRR(G22:G32)</f>
         <v/>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="37">
         <f>IRR(H22:H32)</f>
         <v/>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="37">
         <f>IRR(I22:I32)</f>
         <v/>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="37">
         <f>IRR(J22:J32)</f>
         <v/>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="37">
         <f>IRR(K22:K32)</f>
         <v/>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="37">
         <f>IRR(L22:L32)</f>
         <v/>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="37">
         <f>IRR(M22:M32)</f>
         <v/>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="37">
         <f>IRR(N22:N32)</f>
         <v/>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="37">
         <f>IRR(O22:O32)</f>
         <v/>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="37">
         <f>IRR(P22:P32)</f>
         <v/>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="37">
         <f>IRR(Q22:Q32)</f>
         <v/>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="37">
         <f>IRR(R22:R32)</f>
         <v/>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="37">
         <f>IRR(S22:S32)</f>
         <v/>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="37">
         <f>IRR(T22:T32)</f>
         <v/>
       </c>
-      <c r="U33" s="35">
+      <c r="U33" s="37">
         <f>IRR(U22:U32)</f>
         <v/>
       </c>
-      <c r="V33" s="35">
+      <c r="V33" s="37">
         <f>IRR(V22:V32)</f>
         <v/>
       </c>
-      <c r="W33" s="35">
+      <c r="W33" s="37">
         <f>IRR(W22:W32)</f>
         <v/>
       </c>
-      <c r="X33" s="35">
+      <c r="X33" s="37">
         <f>IRR(X22:X32)</f>
         <v/>
       </c>
-      <c r="Y33" s="35">
+      <c r="Y33" s="37">
         <f>IRR(Y22:Y32)</f>
         <v/>
       </c>
-      <c r="Z33" s="35">
+      <c r="Z33" s="37">
         <f>IRR(Z22:Z32)</f>
         <v/>
       </c>
@@ -3558,7 +3566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:O104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3574,6 +3582,7 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4113,6 +4122,13 @@
       <c r="I16" s="23" t="n"/>
       <c r="J16" s="23" t="n"/>
       <c r="K16" s="22" t="n"/>
+      <c r="M16" s="27" t="inlineStr">
+        <is>
+          <t>OTHER INCOME  (monthly recurring)</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="n"/>
+      <c r="O16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="22" t="n">
@@ -4146,6 +4162,21 @@
       <c r="I17" s="23" t="n"/>
       <c r="J17" s="23" t="n"/>
       <c r="K17" s="22" t="n"/>
+      <c r="M17" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="N17" s="28" t="inlineStr">
+        <is>
+          <t>Monthly $</t>
+        </is>
+      </c>
+      <c r="O17" s="28" t="inlineStr">
+        <is>
+          <t>Annual $</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="22" t="n">
@@ -4179,6 +4210,18 @@
       <c r="I18" s="23" t="n"/>
       <c r="J18" s="23" t="n"/>
       <c r="K18" s="22" t="n"/>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>RUBS / Utility Reimbursement</t>
+        </is>
+      </c>
+      <c r="N18" s="17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O18" s="12">
+        <f>N18*12</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n">
@@ -4212,6 +4255,18 @@
       <c r="I19" s="23" t="n"/>
       <c r="J19" s="23" t="n"/>
       <c r="K19" s="22" t="n"/>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>Laundry / Vending</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="n">
+        <v>700</v>
+      </c>
+      <c r="O19" s="12">
+        <f>N19*12</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="n">
@@ -4245,6 +4300,18 @@
       <c r="I20" s="23" t="n"/>
       <c r="J20" s="23" t="n"/>
       <c r="K20" s="22" t="n"/>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>Pet Rent</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="n">
+        <v>900</v>
+      </c>
+      <c r="O20" s="12">
+        <f>N20*12</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="22" t="n">
@@ -4278,6 +4345,18 @@
       <c r="I21" s="23" t="n"/>
       <c r="J21" s="23" t="n"/>
       <c r="K21" s="22" t="n"/>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>Parking / Storage</t>
+        </is>
+      </c>
+      <c r="N21" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="O21" s="12">
+        <f>N21*12</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="n">
@@ -4311,6 +4390,18 @@
       <c r="I22" s="23" t="n"/>
       <c r="J22" s="23" t="n"/>
       <c r="K22" s="22" t="n"/>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>Application / Admin Fees</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="O22" s="12">
+        <f>N22*12</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="22" t="n">
@@ -4344,6 +4435,18 @@
       <c r="I23" s="23" t="n"/>
       <c r="J23" s="23" t="n"/>
       <c r="K23" s="22" t="n"/>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>Late Fees</t>
+        </is>
+      </c>
+      <c r="N23" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="O23" s="12">
+        <f>N23*12</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="22" t="n">
@@ -4377,6 +4480,12 @@
       <c r="I24" s="23" t="n"/>
       <c r="J24" s="23" t="n"/>
       <c r="K24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="17" t="n"/>
+      <c r="O24" s="12">
+        <f>N24*12</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="22" t="n">
@@ -4410,6 +4519,12 @@
       <c r="I25" s="23" t="n"/>
       <c r="J25" s="23" t="n"/>
       <c r="K25" s="22" t="n"/>
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="17" t="n"/>
+      <c r="O25" s="12">
+        <f>N25*12</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="22" t="n">
@@ -4443,6 +4558,19 @@
       <c r="I26" s="23" t="n"/>
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="22" t="n"/>
+      <c r="M26" s="29" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="N26" s="26">
+        <f>SUM(N18:N25)</f>
+        <v/>
+      </c>
+      <c r="O26" s="30">
+        <f>SUM(O18:O25)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="22" t="n">
@@ -4509,6 +4637,13 @@
       <c r="I28" s="23" t="n"/>
       <c r="J28" s="23" t="n"/>
       <c r="K28" s="22" t="n"/>
+      <c r="M28" s="27" t="inlineStr">
+        <is>
+          <t>CONCESSIONS  (monthly, contra-revenue)</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="n"/>
+      <c r="O28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="22" t="n">
@@ -4542,6 +4677,21 @@
       <c r="I29" s="23" t="n"/>
       <c r="J29" s="23" t="n"/>
       <c r="K29" s="22" t="n"/>
+      <c r="M29" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="N29" s="28" t="inlineStr">
+        <is>
+          <t>Monthly $</t>
+        </is>
+      </c>
+      <c r="O29" s="28" t="inlineStr">
+        <is>
+          <t>Annual $</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="22" t="n">
@@ -4575,6 +4725,16 @@
       <c r="I30" s="23" t="n"/>
       <c r="J30" s="23" t="n"/>
       <c r="K30" s="22" t="n"/>
+      <c r="M30" s="22" t="inlineStr">
+        <is>
+          <t>e.g., 1 mo free (amortized)</t>
+        </is>
+      </c>
+      <c r="N30" s="17" t="n"/>
+      <c r="O30" s="12">
+        <f>N30*12</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="22" t="n">
@@ -4608,6 +4768,16 @@
       <c r="I31" s="23" t="n"/>
       <c r="J31" s="23" t="n"/>
       <c r="K31" s="22" t="n"/>
+      <c r="M31" s="22" t="inlineStr">
+        <is>
+          <t>e.g., look-and-lease</t>
+        </is>
+      </c>
+      <c r="N31" s="17" t="n"/>
+      <c r="O31" s="12">
+        <f>N31*12</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="22" t="n">
@@ -4641,6 +4811,12 @@
       <c r="I32" s="23" t="n"/>
       <c r="J32" s="23" t="n"/>
       <c r="K32" s="22" t="n"/>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="17" t="n"/>
+      <c r="O32" s="12">
+        <f>N32*12</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="22" t="n">
@@ -4674,6 +4850,12 @@
       <c r="I33" s="23" t="n"/>
       <c r="J33" s="23" t="n"/>
       <c r="K33" s="22" t="n"/>
+      <c r="M33" s="22" t="n"/>
+      <c r="N33" s="17" t="n"/>
+      <c r="O33" s="12">
+        <f>N33*12</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="n">
@@ -4707,6 +4889,12 @@
       <c r="I34" s="23" t="n"/>
       <c r="J34" s="23" t="n"/>
       <c r="K34" s="22" t="n"/>
+      <c r="M34" s="22" t="n"/>
+      <c r="N34" s="17" t="n"/>
+      <c r="O34" s="12">
+        <f>N34*12</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="22" t="n">
@@ -4740,6 +4928,19 @@
       <c r="I35" s="23" t="n"/>
       <c r="J35" s="23" t="n"/>
       <c r="K35" s="22" t="n"/>
+      <c r="M35" s="29" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="N35" s="26">
+        <f>SUM(N30:N34)</f>
+        <v/>
+      </c>
+      <c r="O35" s="30">
+        <f>SUM(O30:O34)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="n">
@@ -4806,6 +5007,13 @@
       <c r="I37" s="23" t="n"/>
       <c r="J37" s="23" t="n"/>
       <c r="K37" s="22" t="n"/>
+      <c r="M37" s="27" t="inlineStr">
+        <is>
+          <t>EMPLOYEE / MODEL DISCOUNTS  (monthly)</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="22" t="n">
@@ -4839,6 +5047,21 @@
       <c r="I38" s="23" t="n"/>
       <c r="J38" s="23" t="n"/>
       <c r="K38" s="22" t="n"/>
+      <c r="M38" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="N38" s="28" t="inlineStr">
+        <is>
+          <t>Monthly $</t>
+        </is>
+      </c>
+      <c r="O38" s="28" t="inlineStr">
+        <is>
+          <t>Annual $</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="22" t="n">
@@ -4872,6 +5095,16 @@
       <c r="I39" s="23" t="n"/>
       <c r="J39" s="23" t="n"/>
       <c r="K39" s="22" t="n"/>
+      <c r="M39" s="22" t="inlineStr">
+        <is>
+          <t>e.g., on-site staff units</t>
+        </is>
+      </c>
+      <c r="N39" s="17" t="n"/>
+      <c r="O39" s="12">
+        <f>N39*12</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="n">
@@ -4905,6 +5138,16 @@
       <c r="I40" s="23" t="n"/>
       <c r="J40" s="23" t="n"/>
       <c r="K40" s="22" t="n"/>
+      <c r="M40" s="22" t="inlineStr">
+        <is>
+          <t>e.g., model unit</t>
+        </is>
+      </c>
+      <c r="N40" s="17" t="n"/>
+      <c r="O40" s="12">
+        <f>N40*12</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="n">
@@ -4938,6 +5181,12 @@
       <c r="I41" s="23" t="n"/>
       <c r="J41" s="23" t="n"/>
       <c r="K41" s="22" t="n"/>
+      <c r="M41" s="22" t="n"/>
+      <c r="N41" s="17" t="n"/>
+      <c r="O41" s="12">
+        <f>N41*12</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="n">
@@ -4971,6 +5220,12 @@
       <c r="I42" s="23" t="n"/>
       <c r="J42" s="23" t="n"/>
       <c r="K42" s="22" t="n"/>
+      <c r="M42" s="22" t="n"/>
+      <c r="N42" s="17" t="n"/>
+      <c r="O42" s="12">
+        <f>N42*12</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="22" t="n">
@@ -5004,6 +5259,12 @@
       <c r="I43" s="23" t="n"/>
       <c r="J43" s="23" t="n"/>
       <c r="K43" s="22" t="n"/>
+      <c r="M43" s="22" t="n"/>
+      <c r="N43" s="17" t="n"/>
+      <c r="O43" s="12">
+        <f>N43*12</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="22" t="n">
@@ -5037,6 +5298,19 @@
       <c r="I44" s="23" t="n"/>
       <c r="J44" s="23" t="n"/>
       <c r="K44" s="22" t="n"/>
+      <c r="M44" s="29" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="N44" s="26">
+        <f>SUM(N39:N43)</f>
+        <v/>
+      </c>
+      <c r="O44" s="30">
+        <f>SUM(O39:O43)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="22" t="n">
@@ -7556,7 +7830,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Total / Weighted</t>
         </is>
@@ -7577,36 +7851,36 @@
         <f>IFERROR(H16/B16,0)</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="30">
         <f>SUM(F4:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="30">
         <f>SUM(G4:G15)</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="30">
         <f>SUM(H4:H15)</f>
         <v/>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="30">
         <f>SUM(I4:I15)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Loss-to-Lease (Market - In-Place, annual)</t>
         </is>
       </c>
-      <c r="I18" s="30">
+      <c r="I18" s="32">
         <f>I16-G16</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Units in Rent Roll (all rows)</t>
         </is>
@@ -7617,12 +7891,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Check: mapped = rent roll?</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="29">
         <f>IF(B16='Rent Roll (Input)'!$N$7,"OK — all units mapped","ADD missing floor plan(s) to col A")</f>
         <v/>
       </c>
@@ -7801,26 +8075,26 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="30">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="30">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Blended cost / renovated unit</t>
         </is>
@@ -7848,39 +8122,39 @@
       <c r="K12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B13" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="32" t="n">
+      <c r="B13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="32" t="n">
+      <c r="H13" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="I13" s="32" t="n">
+      <c r="I13" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="32" t="n">
+      <c r="J13" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="K13" s="32" t="n">
+      <c r="K13" s="34" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7927,43 +8201,43 @@
           <t>Cumulative Units Renovated</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="35">
         <f>$B$9*B14</f>
         <v/>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="35">
         <f>$B$9*C14</f>
         <v/>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="35">
         <f>$B$9*D14</f>
         <v/>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="35">
         <f>$B$9*E14</f>
         <v/>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="35">
         <f>$B$9*F14</f>
         <v/>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="35">
         <f>$B$9*G14</f>
         <v/>
       </c>
-      <c r="H15" s="33">
+      <c r="H15" s="35">
         <f>$B$9*H14</f>
         <v/>
       </c>
-      <c r="I15" s="33">
+      <c r="I15" s="35">
         <f>$B$9*I14</f>
         <v/>
       </c>
-      <c r="J15" s="33">
+      <c r="J15" s="35">
         <f>$B$9*J14</f>
         <v/>
       </c>
-      <c r="K15" s="33">
+      <c r="K15" s="35">
         <f>$B$9*K14</f>
         <v/>
       </c>
@@ -8063,7 +8337,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>Net Premium to EGI</t>
         </is>
@@ -8184,15 +8458,13 @@
           <t>Gross Potential Rent (GPR)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>'RR'!$G$16</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>'RR'!$I$16</t>
-        </is>
+      <c r="B5" s="19">
+        <f>'RR'!$G$16</f>
+        <v/>
+      </c>
+      <c r="C5" s="19">
+        <f>'RR'!$I$16</f>
+        <v/>
       </c>
       <c r="D5" s="12">
         <f>C5/'RR'!$B$16</f>
@@ -8231,11 +8503,11 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Less: Bad Debt &amp; Concessions</t>
+          <t>Less: Bad Debt / Concessions / Empl. Disc.</t>
         </is>
       </c>
       <c r="B7" s="12">
-        <f>-B5*'Assumptions'!$B$17</f>
+        <f>-('Rent Roll (Input)'!$O$35+'Rent Roll (Input)'!$O$44)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -8246,9 +8518,14 @@
         <f>C7/'RR'!$B$16</f>
         <v/>
       </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>In-place: actual concessions + employee discounts from Rent Roll (Input). UW: bad-debt &amp; concession % (Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Net Rental Income</t>
         </is>
@@ -8272,8 +8549,9 @@
           <t>Other Income (RUBS, fees, laundry)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
-        <v>90000</v>
+      <c r="B9" s="19">
+        <f>'Rent Roll (Input)'!$O$26</f>
+        <v/>
       </c>
       <c r="C9" s="12">
         <f>B9*(1+'Assumptions'!$B$14)</f>
@@ -8285,12 +8563,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>Type T-12 actual; UW grows it one year.</t>
+          <t>In-place pulls the Other Income section on Rent Roll (Input); UW grows it one year.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Effective Gross Income (EGI)</t>
         </is>
@@ -8512,16 +8790,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="30">
         <f>SUM(B13:B22)</f>
         <v/>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="30">
         <f>SUM(C13:C22)</f>
         <v/>
       </c>
@@ -8531,16 +8809,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>NET OPERATING INCOME (NOI)</t>
         </is>
       </c>
-      <c r="B24" s="34">
+      <c r="B24" s="36">
         <f>B10-B23</f>
         <v/>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="36">
         <f>C10-C23</f>
         <v/>
       </c>
@@ -8555,11 +8833,11 @@
           <t>Operating Expense Ratio</t>
         </is>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="37">
         <f>B23/B10</f>
         <v/>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="37">
         <f>C23/C10</f>
         <v/>
       </c>
@@ -8753,7 +9031,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Effective Gross Income</t>
         </is>
@@ -8847,102 +9125,102 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="30">
         <f>B6-B7</f>
         <v/>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="30">
         <f>C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="30">
         <f>D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="30">
         <f>E6-E7</f>
         <v/>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="30">
         <f>F6-F7</f>
         <v/>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="30">
         <f>G6-G7</f>
         <v/>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="30">
         <f>H6-H7</f>
         <v/>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="30">
         <f>I6-I7</f>
         <v/>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="30">
         <f>J6-J7</f>
         <v/>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="30">
         <f>K6-K7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>NOI Growth %</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="37">
         <f>C8/B8-1</f>
         <v/>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="37">
         <f>D8/C8-1</f>
         <v/>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="37">
         <f>E8/D8-1</f>
         <v/>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="37">
         <f>F8/E8-1</f>
         <v/>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="37">
         <f>G8/F8-1</f>
         <v/>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="37">
         <f>H8/G8-1</f>
         <v/>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="37">
         <f>I8/H8-1</f>
         <v/>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="37">
         <f>J8/I8-1</f>
         <v/>
       </c>
-      <c r="K9" s="35">
+      <c r="K9" s="37">
         <f>K8/J8-1</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>(memo) Reno Capex Draw</t>
         </is>
@@ -9060,12 +9338,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Total Uses</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="30">
         <f>SUM(B4:B6)</f>
         <v/>
       </c>
@@ -9088,7 +9366,7 @@
         <f>'Assumptions'!$B$4*'Assumptions'!$B$22</f>
         <v/>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="37">
         <f>B10/B7</f>
         <v/>
       </c>
@@ -9107,7 +9385,7 @@
         <f>B7-B10</f>
         <v/>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="37">
         <f>B11/B7</f>
         <v/>
       </c>
@@ -9117,18 +9395,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Total Sources</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="30">
         <f>SUM(B10:B11)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Check (Sources - Uses)</t>
         </is>
@@ -9189,7 +9467,7 @@
           <t>Interest Rate</t>
         </is>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="39">
         <f>'Assumptions'!$B$23</f>
         <v/>
       </c>
@@ -9238,7 +9516,7 @@
           <t>Monthly Amortizing Payment</t>
         </is>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="40">
         <f>PMT(B5/12,B6*12,-B4)</f>
         <v/>
       </c>
@@ -9265,12 +9543,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Annual Debt Service — Amortizing</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="41">
         <f>B9*12</f>
         <v/>
       </c>
@@ -9286,7 +9564,7 @@
           <t>DSCR — Year 1 (actual)</t>
         </is>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="42">
         <f>'Pro Forma'!$B$8/IF(1&lt;=B7,B10,B11)</f>
         <v/>
       </c>
@@ -9302,7 +9580,7 @@
           <t>DSCR — Amortizing (stress)</t>
         </is>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="42">
         <f>'Pro Forma'!$B$8/B11</f>
         <v/>
       </c>
@@ -9318,7 +9596,7 @@
           <t>Debt Yield (Year-1 NOI)</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>'Pro Forma'!$B$8/B4</f>
         <v/>
       </c>
